--- a/exams_import.xlsx
+++ b/exams_import.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="25726"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\qr-exams-system\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A8DBB16-DFA0-4945-ACA8-270B5491F0E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView xWindow="2244" yWindow="1608" windowWidth="20736" windowHeight="10752" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -18,15 +24,191 @@
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="7">
+  <si>
+    <t>type</t>
+  </si>
+  <si>
+    <t>questions</t>
+  </si>
+  <si>
+    <t>class_id</t>
+  </si>
+  <si>
+    <t>coptic</t>
+  </si>
+  <si>
+    <t>[{ "question": "1- Ⲁ ⲁ", "wight": "3" },
+        { "question": "2- Ⲇ ⲇ", "wight": "3" },
+        { "question": "3- ⲋ ⲋ", "wight": "3" },
+        { "question": "4- Ⲍ ⲍ", "wight": "3" },
+        { "question": "5- Ⲏ ⲏ", "wight": "3" },
+        { "question": "6- Ⲑ ⲑ", "wight": "3" },
+        { "question": "7- Ⲉ ⲉ", "wight": "3" },
+        { "question": "8- Ⳉ ⳉ", "wight": "3" },
+        { "question": "9- Ⲓ ⲓ", "wight": "3" },
+        { "question": "10- Ⲃ ⲃ", "wight": "3" },
+        { "question": "11- ̀Ⲉⲃⲓⲱ عسل", "wight": "5" },
+        { "question": "12- Ⲁⲫⲉ  رأس", "wight": "5" },
+        { "question": "13- Ⲁⲛⳉⳉⲉⲗⲟⲥ  ملاك", "wight": "5" },
+        { "question": "14- Ⲍⲉⲛⲍⲉⲛ  سحلية", "wight": "5" },
+        { "question": "15- Ⲓⲁⲗ مراية", "wight": "5" },
+        { "question": "16- Ⲃⲁⲗ عين", "wight": "5" },
+        { "question": "17- Ⲇⲁⲩⲓⲇ  داود", "wight": "5" },
+        { "question": "18- Ⲑⲉⲗⲏⲗ تهليل", "wight": "5" },
+        { "question": "19- Ⲏⲓ  بيت", "wight": "5" }
+    ]</t>
+  </si>
+  <si>
+    <t>[{ "question": "1-  كلمة رقبة يعني ؟", "wight": "5" },
+{ "question": "2-  اذكر قاعدة حرف Ⳉ ", "wight": "5" },
+{ "question": "3-  كلمة  يعني Ⲟⲩϫⲁⲓ  ؟", "wight": "5" },
+{ "question": "4-  كلمة Ⲛⲁⲛⲉ ⲣⲟⲩϩⲓ يعني ؟", "wight": "5" },
+{ "question": "5-  كلمة رائحة يعني ؟", "wight": "5" },
+{ "question": "6-  اذكر قاعدة حرف ϯ", "wight": "5" },
+{ "question": "7-  كلمة Ⲁⲛⲍⲏⲃ يعني ؟", "wight": "5" },
+{ "question": "8-  عدد الحروف الساكنة  والحروف المتحركة ","wight": "5" },
+{ "question": "9-  كلمة فول يعني ؟", "wight": "5" },
+{ "question": "10-  اذكر قاعدة حرف Ⲩ", "wight": "5" },
+{ "question": "11-  كلمة Ⲕⲁϣ يعني ؟", "wight": "5" },
+{ "question": "12-  كلمة داود يعني ؟", "wight": "5" },
+{ "question": "13-  إيه هما الحروف المتحركة القابلة للكسر ؟", "wight": "5" },
+{ "question": "14-  كلمة Ϯⲏⲃ يعني ؟", "wight": "5" },
+{ "question": "15-  كلمة عيد يعني ؟", "wight": "5" },
+{ "question": "16-  كلمة قدم يعني ؟", "wight": "5" },
+{ "question": "17-  كلمة Ⲭⲁⲕⲓ يعني ؟", "wight": "5" },
+{ "question": "18-  صباح الخير يعني ", "wight": "5" }]</t>
+  </si>
+  <si>
+    <t>[{
+		"question": "1-  ( Ϣⲁϣϥ - `Ϣⲙⲏⲛ - Ϣⲁϥⲉ ) رقم 7  تعني",
+		"wight": "2"
+	},
+	{
+		"question": "2-  ( كرسى - غرفة - حائط )  Ϭⲗⲟ تعنى",
+		"wight": "2"
+	},
+	{
+		"question": "3-  ( Ⲥⲟⲩⲣⲓ - Ⲱⲛⲓ - Ⲧⲟⲧⲥ ) شوكة تعني",
+		"wight": "2"
+	},
+	{
+		"question": "4-  ( شباك - شارع - نحلة ) Ⲕⲁⲑⲏⲟⲩ تعني",
+		"wight": "2"
+	},
+	{
+		"question": "5-  ( Ⲕⲁϫⲓ - Ⲯⲩⲭⲟⲥ - Ⲟⲩⲁⲓ ) رقم 1  تعني",
+		"wight": "2"
+	},
+	{
+		"question": "6-  اذكر رقم 7",
+		"wight": "2"
+	},
+	{
+		"question": "7-  اذكر رقم 3",
+		"wight": "2"
+	},
+	{
+		"question": "8-  اذكر رقم 8",
+		"wight": "2"
+	},
+	{
+		"question": "9-  اذكر رقم 9",
+		"wight": "2"
+	},
+	{
+		"question": "10-  اذكر رقم 10",
+		"wight": "2"
+	},
+	{
+		"question": "11- Ⲛ - Ⲏ -  Ⲧ - Ⲟ - Ⲩ - Ⲇ اذكر قاعدة الحروف الآتية : (اختر حرف و لا يكرر فى السوال التالى)",
+		"wight": "4"
+	},
+	{
+		"question": "12- Ⲛ - Ⲏ -  Ⲧ - Ⲟ - Ⲩ - Ⲇ  اذكر قاعدة الحروف الآتية : (اختر حرف و لا يكرر فى السوال التالى)",
+		"wight": "4"
+	},
+	{
+		"question": "13- Ⲛ - Ⲏ -  Ⲧ - Ⲟ - Ⲩ - Ⲇ  اذكر قاعدة الحروف الآتية : (اختر حرف و لا يكرر فى السوال التالى)",
+		"wight": "4"
+	},
+	{
+		"question": "14- Ⲛ - Ⲏ -  Ⲧ - Ⲟ - Ⲩ - Ⲇ  اذكر قاعدة الحروف الآتية : (اختر حرف و لا يكرر فى السوال التالى)",
+		"wight": "4"
+	},
+	{
+		"question": "15- Ⲛ - Ⲏ -  Ⲧ - Ⲟ - Ⲩ - Ⲇ  اذكر قاعدة الحروف الآتية : (اختر حرف و لا يكرر فى السوال التالى)",
+		"wight": "4"
+	},
+	{
+		"question": "16- ",
+		"wight": "3"
+	},
+	{
+		"question": "17-",
+		"wight": "3"
+	},
+	{
+		"question": "18-  رقم 6 ينطف Ϣⲟⲙⲧ",
+		"wight": "3"
+	},
+	{
+		"question": "19-  دانيال يعنى Ⲇⲁⲛⲓⲏⲗ",
+		"wight": "3"
+	},
+	{
+		"question": "20-  سماء يعنى Ⲫⲉ",
+		"wight": "3"
+	},
+	{
+		"question": "21-  حروف اللغة القبطى منقسمين الى 3 اقسام اذكرهم ",
+		"wight": "5"
+	},
+	{
+		"question": "22-  معني حواء",
+		"wight": "5"
+	},
+	{
+		"question": "23-  معني كرسي ",
+		"wight": "5"
+	},
+	{
+		"question": "24-  معنى غرفة",
+		"wight": "5"
+	},
+	{
+		"question": "25-  كم عدد الحروف المتحركة القابلة للكسر؟ وما هم ؟ ",
+		"wight": "5"
+	},
+	{
+		"question": "26-  ما هي اسم العلامة التي توضع فوق الحروف وتنطق ( إ ) أو همزة ؟  ",
+		"wight": "5"
+	},
+	{
+		"question": "27-",
+		"wight": "5"
+	}
+]</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9.8000000000000007"/>
+      <color rgb="FFD4D4D4"/>
+      <name val="JetBrains Mono"/>
+      <family val="3"/>
     </font>
   </fonts>
   <fills count="2">
@@ -49,8 +231,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -330,10 +515,139 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:D9"/>
+  <sheetFormatPr defaultRowHeight="13.95" customHeight="1"/>
+  <cols>
+    <col min="2" max="2" width="14.88671875" customWidth="1"/>
+    <col min="3" max="3" width="13.44140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="13.95" customHeight="1">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="13.95" customHeight="1">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="13.95" customHeight="1">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3">
+        <v>2</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="13.95" customHeight="1">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C4">
+        <v>3</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="13.95" customHeight="1">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C5">
+        <v>4</v>
+      </c>
+      <c r="D5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="13.95" customHeight="1">
+      <c r="A6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C6">
+        <v>5</v>
+      </c>
+      <c r="D6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="13.95" customHeight="1">
+      <c r="A7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C7">
+        <v>6</v>
+      </c>
+      <c r="D7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="13.95" customHeight="1">
+      <c r="A8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C8">
+        <v>7</v>
+      </c>
+      <c r="D8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="13.95" customHeight="1">
+      <c r="A9" t="s">
+        <v>3</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C9">
+        <v>8</v>
+      </c>
+      <c r="D9">
+        <v>3</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/exams_import.xlsx
+++ b/exams_import.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="25726"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="25831"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\qr-exams-system\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\qr\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A8DBB16-DFA0-4945-ACA8-270B5491F0E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7913DD35-FFCD-4A26-B169-25BA9F00F7CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2244" yWindow="1608" windowWidth="20736" windowHeight="10752" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2304" yWindow="1416" windowWidth="20736" windowHeight="10752" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="27">
   <si>
     <t>type</t>
   </si>
@@ -36,167 +36,294 @@
     <t>class_id</t>
   </si>
   <si>
-    <t>coptic</t>
-  </si>
-  <si>
-    <t>[{ "question": "1- Ⲁ ⲁ", "wight": "3" },
-        { "question": "2- Ⲇ ⲇ", "wight": "3" },
-        { "question": "3- ⲋ ⲋ", "wight": "3" },
-        { "question": "4- Ⲍ ⲍ", "wight": "3" },
-        { "question": "5- Ⲏ ⲏ", "wight": "3" },
-        { "question": "6- Ⲑ ⲑ", "wight": "3" },
-        { "question": "7- Ⲉ ⲉ", "wight": "3" },
-        { "question": "8- Ⳉ ⳉ", "wight": "3" },
-        { "question": "9- Ⲓ ⲓ", "wight": "3" },
-        { "question": "10- Ⲃ ⲃ", "wight": "3" },
-        { "question": "11- ̀Ⲉⲃⲓⲱ عسل", "wight": "5" },
-        { "question": "12- Ⲁⲫⲉ  رأس", "wight": "5" },
-        { "question": "13- Ⲁⲛⳉⳉⲉⲗⲟⲥ  ملاك", "wight": "5" },
-        { "question": "14- Ⲍⲉⲛⲍⲉⲛ  سحلية", "wight": "5" },
-        { "question": "15- Ⲓⲁⲗ مراية", "wight": "5" },
-        { "question": "16- Ⲃⲁⲗ عين", "wight": "5" },
-        { "question": "17- Ⲇⲁⲩⲓⲇ  داود", "wight": "5" },
-        { "question": "18- Ⲑⲉⲗⲏⲗ تهليل", "wight": "5" },
-        { "question": "19- Ⲏⲓ  بيت", "wight": "5" }
+    <t>alhan</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>012</t>
+  </si>
+  <si>
+    <t>011</t>
+  </si>
+  <si>
+    <t>022</t>
+  </si>
+  <si>
+    <t>021</t>
+  </si>
+  <si>
+    <t>113</t>
+  </si>
+  <si>
+    <t>112</t>
+  </si>
+  <si>
+    <t>111</t>
+  </si>
+  <si>
+    <t>121</t>
+  </si>
+  <si>
+    <t>[
+        {
+            "question": "1-\tآمين آمين آمين بموتك يارب نبشر (عربى)",
+            "wight": "20"
+        },
+        {
+            "question": "2- حل وإغفر (حتي كلمة الخفية والظاهرة)",
+            "wight": "20"
+        },
+        {
+            "question": "3- صلوا من أجل الإنجيل المقدس (قبطى وعربى)\n (قبطى- 5 درجات)  و (عربى-5 درجات) ",
+            "wight": "10"
+        },
+        {
+            "question": "4- إسطاثى تيه ميه طا فوﭭو ثيه أو ",
+            "wight": "10"
+        },
+        {
+            "question": "5-\tطوبى للرحماء على المساكین ",
+            "wight": "10"
+        },
+        {
+            "question": "6-\tمردات أناجیل أحد الشعانین\n(4مردات * 10 درجات) ",
+            "wight": "40"
+        }
     ]</t>
   </si>
   <si>
-    <t>[{ "question": "1-  كلمة رقبة يعني ؟", "wight": "5" },
-{ "question": "2-  اذكر قاعدة حرف Ⳉ ", "wight": "5" },
-{ "question": "3-  كلمة  يعني Ⲟⲩϫⲁⲓ  ؟", "wight": "5" },
-{ "question": "4-  كلمة Ⲛⲁⲛⲉ ⲣⲟⲩϩⲓ يعني ؟", "wight": "5" },
-{ "question": "5-  كلمة رائحة يعني ؟", "wight": "5" },
-{ "question": "6-  اذكر قاعدة حرف ϯ", "wight": "5" },
-{ "question": "7-  كلمة Ⲁⲛⲍⲏⲃ يعني ؟", "wight": "5" },
-{ "question": "8-  عدد الحروف الساكنة  والحروف المتحركة ","wight": "5" },
-{ "question": "9-  كلمة فول يعني ؟", "wight": "5" },
-{ "question": "10-  اذكر قاعدة حرف Ⲩ", "wight": "5" },
-{ "question": "11-  كلمة Ⲕⲁϣ يعني ؟", "wight": "5" },
-{ "question": "12-  كلمة داود يعني ؟", "wight": "5" },
-{ "question": "13-  إيه هما الحروف المتحركة القابلة للكسر ؟", "wight": "5" },
-{ "question": "14-  كلمة Ϯⲏⲃ يعني ؟", "wight": "5" },
-{ "question": "15-  كلمة عيد يعني ؟", "wight": "5" },
-{ "question": "16-  كلمة قدم يعني ؟", "wight": "5" },
-{ "question": "17-  كلمة Ⲭⲁⲕⲓ يعني ؟", "wight": "5" },
-{ "question": "18-  صباح الخير يعني ", "wight": "5" }]</t>
-  </si>
-  <si>
-    <t>[{
-		"question": "1-  ( Ϣⲁϣϥ - `Ϣⲙⲏⲛ - Ϣⲁϥⲉ ) رقم 7  تعني",
-		"wight": "2"
-	},
-	{
-		"question": "2-  ( كرسى - غرفة - حائط )  Ϭⲗⲟ تعنى",
-		"wight": "2"
-	},
-	{
-		"question": "3-  ( Ⲥⲟⲩⲣⲓ - Ⲱⲛⲓ - Ⲧⲟⲧⲥ ) شوكة تعني",
-		"wight": "2"
-	},
-	{
-		"question": "4-  ( شباك - شارع - نحلة ) Ⲕⲁⲑⲏⲟⲩ تعني",
-		"wight": "2"
-	},
-	{
-		"question": "5-  ( Ⲕⲁϫⲓ - Ⲯⲩⲭⲟⲥ - Ⲟⲩⲁⲓ ) رقم 1  تعني",
-		"wight": "2"
-	},
-	{
-		"question": "6-  اذكر رقم 7",
-		"wight": "2"
-	},
-	{
-		"question": "7-  اذكر رقم 3",
-		"wight": "2"
-	},
-	{
-		"question": "8-  اذكر رقم 8",
-		"wight": "2"
-	},
-	{
-		"question": "9-  اذكر رقم 9",
-		"wight": "2"
-	},
-	{
-		"question": "10-  اذكر رقم 10",
-		"wight": "2"
-	},
-	{
-		"question": "11- Ⲛ - Ⲏ -  Ⲧ - Ⲟ - Ⲩ - Ⲇ اذكر قاعدة الحروف الآتية : (اختر حرف و لا يكرر فى السوال التالى)",
-		"wight": "4"
-	},
-	{
-		"question": "12- Ⲛ - Ⲏ -  Ⲧ - Ⲟ - Ⲩ - Ⲇ  اذكر قاعدة الحروف الآتية : (اختر حرف و لا يكرر فى السوال التالى)",
-		"wight": "4"
-	},
-	{
-		"question": "13- Ⲛ - Ⲏ -  Ⲧ - Ⲟ - Ⲩ - Ⲇ  اذكر قاعدة الحروف الآتية : (اختر حرف و لا يكرر فى السوال التالى)",
-		"wight": "4"
-	},
-	{
-		"question": "14- Ⲛ - Ⲏ -  Ⲧ - Ⲟ - Ⲩ - Ⲇ  اذكر قاعدة الحروف الآتية : (اختر حرف و لا يكرر فى السوال التالى)",
-		"wight": "4"
-	},
-	{
-		"question": "15- Ⲛ - Ⲏ -  Ⲧ - Ⲟ - Ⲩ - Ⲇ  اذكر قاعدة الحروف الآتية : (اختر حرف و لا يكرر فى السوال التالى)",
-		"wight": "4"
-	},
-	{
-		"question": "16- ",
-		"wight": "3"
-	},
-	{
-		"question": "17-",
-		"wight": "3"
-	},
-	{
-		"question": "18-  رقم 6 ينطف Ϣⲟⲙⲧ",
-		"wight": "3"
-	},
-	{
-		"question": "19-  دانيال يعنى Ⲇⲁⲛⲓⲏⲗ",
-		"wight": "3"
-	},
-	{
-		"question": "20-  سماء يعنى Ⲫⲉ",
-		"wight": "3"
-	},
-	{
-		"question": "21-  حروف اللغة القبطى منقسمين الى 3 اقسام اذكرهم ",
-		"wight": "5"
-	},
-	{
-		"question": "22-  معني حواء",
-		"wight": "5"
-	},
-	{
-		"question": "23-  معني كرسي ",
-		"wight": "5"
-	},
-	{
-		"question": "24-  معنى غرفة",
-		"wight": "5"
-	},
-	{
-		"question": "25-  كم عدد الحروف المتحركة القابلة للكسر؟ وما هم ؟ ",
-		"wight": "5"
-	},
-	{
-		"question": "26-  ما هي اسم العلامة التي توضع فوق الحروف وتنطق ( إ ) أو همزة ؟  ",
-		"wight": "5"
-	},
-	{
-		"question": "27-",
-		"wight": "5"
-	}
-]</t>
+    <t>[
+        {
+            "question": "1-\tآمين آمين آمين بموتك يارب نبشر (عربى)",
+            "wight": "20"
+        },
+        {
+            "question": "2- حل وإغفر\n(حتي كلمة الخفية والظاهرة)",
+            "wight": "20"
+        },
+        {
+            "question": "3- بشفاعات والدة الإله ",
+            "wight": "10"
+        },
+        {
+            "question": "4-  الشاروبيم يسجدون لك ",
+            "wight": "10"
+        }
+    ]</t>
+  </si>
+  <si>
+    <t>[
+        {
+            "question": "1-\tإيه بى إبروس إيـﭭشى إسطاثى تيه",
+            "wight": "5"
+        },
+        {
+            "question": "2- إبروس إيڤ إكصاستيه ",
+            "wight": "5"
+        },
+        {
+            "question": "3- بشفاعات والدة الإله ",
+            "wight": "10"
+        },
+        {
+            "question": "4- الشاروبيم يسجدون لك ",
+            "wight": "10"
+        },
+        {
+            "question": "5-\tأيها الجلوس قفوا (عربى) ",
+            "wight": "5"
+        },
+        {
+            "question": "6-\tوإلى الشرق أنظروا (عربى) ",
+            "wight": "5"
+        },
+        {
+            "question": "7-\tننصت (قبطي وعربي) \n(قبطى- 2.5 درجة)  و (عربى-2.5 درجة)",
+            "wight": "5"
+        },
+        {
+            "question": "8-\tأسجدوا لله بخوف ورعدة (عربى) ",
+            "wight": "5"
+        },
+        {
+            "question": "9-\tننصت آمين (قبطى وعربى)\n (قبطى- 5 درجات)  و (عربى-5 درجات)",
+            "wight": "10"
+        },
+        {
+            "question": "10-\tآمين آمين صلوا (قبطى وعربى)\n (قبطى- 5 درجات)  و (عربى-5 درجات)  ",
+            "wight": "10"
+        }
+    ]</t>
+  </si>
+  <si>
+    <t>[
+        {
+            "question": "1-\tالليلويا فاى بيه بى",
+            "wight": "20"
+        },
+        {
+            "question": "2- تى شورى",
+            "wight": "20"
+        },
+        {
+            "question": "3- هيتينية السيدة العذراء مريم ",
+            "wight": "5"
+        },
+        {
+            "question": "4-   هيتينية الملائكة ",
+            "wight": "5"
+        },
+        {
+            "question": "4-   هيتينية ماريوحنا المعمدان ",
+            "wight": "5"
+        }
+    ]</t>
+  </si>
+  <si>
+    <t>[
+        {
+            "question": "1-\tالليلويا ﭽيه إف ميـﭭـى",
+            "wight": "15"
+        },
+        {
+            "question": "2- هيتينية الرسل، هيتينية مارمرقس\n(2*5 درجات)",
+            "wight": "10"
+        },
+        {
+            "question": "3- هيتينية القديس إسطفانوس، هيتينية مارجرجس\n(2*5 درجات) ",
+            "wight": "5"
+        },
+        {
+            "question": "4-   هيتينية أبو سيفين، هيتينية مارمينا\n(2*5 درجات) ",
+            "wight": "5"
+        },
+        {
+            "question": "5-   هيتينية القديسة دميانة، هيتينية الأنبا بيشوى\n(2*5 درجات) ",
+            "wight": "5"
+        },
+        {
+            "question": "6-   هيتينية الأنبا كاراس، هيتينية ق. كسيموس ودوماديوس\n(2*5 درجات) ",
+            "wight": "5"
+        },
+        {
+            "question": "7-   هيتينية قديسى اليوم، هيتينية البابا\n(2*5 درجات) ",
+            "wight": "5"
+        },
+        {
+            "question": "8-  هيتينية الأسقف ",
+            "wight": "5"
+        },
+        {
+            "question": "9-  هيتين ني إبريسـﭭيا (الختام الباسيلي السريع) ",
+            "wight": "5"
+        }
+    ]</t>
+  </si>
+  <si>
+    <t>[
+        {
+            "question": "1-\tإسباتير آجيوس",
+            "wight": "15"
+        },
+        {
+            "question": "2- الليلويا فاى بيه بى",
+            "wight": "15"
+        },
+        {
+            "question": "3- الليلويا ﭽيه إف ميـﭭـى ",
+            "wight": "15"
+        },
+        {
+            "question": "4- تى شورى ",
+            "wight": "20"
+        },
+        {
+            "question": "5-\tهيتينية السيدة العذراء مريم، هيتينية الملائكة\n(2 * 5= 10) ",
+            "wight": "10"
+        },
+        {
+            "question": "6-\t هيتينية ماريوحنا المعمدان، هيتينية الرسل\n(2 * 5= 10)",
+            "wight": "10"
+        },
+        {
+            "question": "7-\t هيتين نى إبريسـﭭيا (الختام الباسيلى السريع)",
+            "wight": "15"
+        }
+    ]</t>
+  </si>
+  <si>
+    <t>[
+        {
+            "question": "1-\tأوشية السلام (عربى)",
+            "wight": "5"
+        },
+        {
+            "question": "2- أوشية الآباء (عربى)- عشية وباكر وقداس.",
+            "wight": "10"
+        },
+        {
+            "question": "3- أوشية المرضى (عربى) ",
+            "wight": "10"
+        },
+        {
+            "question": "4-  أوشية المسافرين (عربى) ",
+            "wight": "10"
+        },
+        {
+            "question": "5-\tأوشية الموضع (قبطى وعربى) - عشية وباكر وقداس\n(5 درجات عربي) و (10 درجات قبطي) ",
+            "wight": "15"
+        },
+        {
+            "question": "6-\t أوشية الاجتماعات (قبطى، عربى)\n(5 درجات عربي) و (10 درجات قبطي)",
+            "wight": "15"
+        },
+        {
+            "question": "7-\t تين جوشت إيـﭭول خا إتهى (عشية وباكر وقداس)\n(10 درجات عشية وباكر) و (10 درجات قداس)",
+            "wight": "20"
+        },
+        {
+            "question": "8-\t مرد إنجيل باكر السنوي (مارين أو أوأوشت)",
+            "wight": "10"
+        },
+        {
+            "question": "9-\t ﭭـول إيـﭭول",
+            "wight": "20"
+        },
+        {
+            "question": "10-\t مزمور التوزيع السنوى (عربى)\n(تسميع 5 أرباع فقط) - (5*5=25)",
+            "wight": "25"
+        }
+    ]</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -205,9 +332,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9.8000000000000007"/>
-      <color rgb="FFD4D4D4"/>
-      <name val="JetBrains Mono"/>
+      <sz val="8"/>
+      <color rgb="FFABB2BF"/>
+      <name val="Consolas"/>
       <family val="3"/>
     </font>
   </fonts>
@@ -231,8 +358,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -516,14 +644,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D9"/>
-  <sheetFormatPr defaultRowHeight="13.95" customHeight="1"/>
+  <dimension ref="A1:F9"/>
+  <sheetFormatPr defaultRowHeight="13.95" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="14.88671875" customWidth="1"/>
     <col min="3" max="3" width="13.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="13.95" customHeight="1">
+    <row r="1" spans="1:6" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -534,116 +662,164 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="13.95" customHeight="1">
+    <row r="2" spans="1:6" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="1" t="s">
-        <v>4</v>
+      <c r="B2" s="2" t="s">
+        <v>21</v>
       </c>
       <c r="C2">
         <v>1</v>
       </c>
-      <c r="D2">
-        <v>1</v>
+      <c r="D2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="13.95" customHeight="1">
+    <row r="3" spans="1:6" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>4</v>
+      <c r="B3" s="2" t="s">
+        <v>22</v>
       </c>
       <c r="C3">
         <v>2</v>
       </c>
-      <c r="D3">
-        <v>1</v>
+      <c r="D3" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="13.95" customHeight="1">
+    <row r="4" spans="1:6" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="1" t="s">
-        <v>4</v>
+      <c r="B4" s="2" t="s">
+        <v>23</v>
       </c>
       <c r="C4">
         <v>3</v>
       </c>
-      <c r="D4">
-        <v>1</v>
+      <c r="D4" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="13.95" customHeight="1">
+    <row r="5" spans="1:6" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="1" t="s">
-        <v>4</v>
+      <c r="B5" s="2" t="s">
+        <v>20</v>
       </c>
       <c r="C5">
         <v>4</v>
       </c>
-      <c r="D5">
-        <v>1</v>
+      <c r="D5" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="13.95" customHeight="1">
+    <row r="6" spans="1:6" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>3</v>
       </c>
-      <c r="B6" s="1" t="s">
-        <v>6</v>
+      <c r="B6" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="C6">
         <v>5</v>
       </c>
-      <c r="D6">
-        <v>2</v>
+      <c r="D6" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>16</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="13.95" customHeight="1">
+    <row r="7" spans="1:6" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>3</v>
       </c>
-      <c r="B7" s="1" t="s">
-        <v>6</v>
+      <c r="B7" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="C7">
         <v>6</v>
       </c>
-      <c r="D7">
-        <v>2</v>
+      <c r="D7" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>17</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="13.95" customHeight="1">
+    <row r="8" spans="1:6" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>3</v>
       </c>
-      <c r="B8" s="1" t="s">
-        <v>6</v>
+      <c r="B8" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="C8">
         <v>7</v>
       </c>
-      <c r="D8">
-        <v>2</v>
+      <c r="D8" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>18</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="13.95" customHeight="1">
+    <row r="9" spans="1:6" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>3</v>
       </c>
-      <c r="B9" s="1" t="s">
-        <v>5</v>
+      <c r="B9" s="2" t="s">
+        <v>26</v>
       </c>
       <c r="C9">
         <v>8</v>
       </c>
-      <c r="D9">
-        <v>3</v>
+      <c r="D9" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>19</v>
       </c>
     </row>
   </sheetData>

--- a/exams_import.xlsx
+++ b/exams_import.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\MY_WORK\peter\qr-exams-system\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21EB4D0F-F089-4873-ADAE-FD96547C9168}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E627841-D79E-432A-9439-00245335C4E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5760" yWindow="2268" windowWidth="17280" windowHeight="8964" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,15 +39,6 @@
     <t>taks</t>
   </si>
   <si>
-    <t>[         {             "question": "1- تكون القربانة على شكل (دائرة)، وليه دائرة؟ (علشان ملهاش بداية ولا نهاية ذى بابا يسوع)، والكلام القبطى المكتوب عليها اسمه إيه؟ (تسبحه الملائكة) وكلماته إيه؟ (قدوس الله – قدوس القوى – قدوس الحى الذى لا يموت).",             "wight": "8"         },         {             "question": "2- تُعْجَن وتخبز القربانة فى مكان اسمه  (بيت لحم)",             "wight": "2"         },         {             "question": "3- أثناء خَبْز القربانة بنصلى (مزامير) علشان فيها (إشارات عن مجئ بابا يسوع)",             "wight": "4"         },         {             "question": "4- عجين القربانة يُخْبَز من دقيق (القمح)، والسبب  في كدة إنه (أنقى أنواع الدقيق ذى ما بابا يسوع هو نقى)، ومش بنحط ملح فى العجينه علشان (الملح بيظبط الأكل وبابا يسوع مش محتاج حاجه تظبطه)، وبنحط خميره علشان (الخميره بترفع العجينة ذى ما بابا يسوع رفع الخطيه عننا علي الصليب)",             "wight": "8"         },         {             "question": "5- عدد القربان إللى بيبقى فى طبق الحمل  هو (3 – 5 – 7 – عدد فردى)",             "wight": "2"         },         {             "question": "6- المنارة بيبقي جواها (جرس) وفوقيها (صليب) رمز (انتصارنا على الشيطان)",             "wight": "6"         },         {             "question": "7- الشماس بيلبس (تونية)، ولونها (أبيض ذى الثلج)، وليه لونها أبيض؟ (ذى لون لبس بابا يسوع فى التجلى)",             "wight": "6"         },         {             "question": "8- البطرشيل لونه (أحمر) ومأخوذ من كلمة يونانية معناها ( نعمة)",             "wight": "4"         },         {             "question": "9- اذكر رتب الشمامسه ومعناها؟\n 1. الإبصالتس ومعناها المرتل.\n 2. الاغنسطس ومعناها قارئ\n 3. الايبودياكون ومعناها مساعد الشماس\n 4. الدياكون ومعناها الشماس الكامل.\n 5. الارشيدياكون ومعناها رئيس الشمامسة.",             "wight": "20"         },         {             "question": "10- سمع: \nقدوس الله، قدوس القوى، قدوس الحي الذي لا يموت، الذي ولد من العذراء، ارحمنا. قدوس الله، قدوس القوى، قدوس الحي الذي لا يموت، الذي صلب عنا، ارحمنا. قدوس الله، قدوس القوى، قدوس الحي الذي لا يموت، الذي قام من الأموات وصعد إلى السموات، ارحمنا. المجد للآب والابن والروح القدس، الآن وكل أوان وإلى دهر الدهور. آمين. أيها الثالوث القدوس ارحمنا. أيها الثالوث القدوس ارحمنا. أيها الثالوث القدوس ارحمنا. يا رب اغفر لنا خطايانا. يا رب اغفر لنا آثامنا. يا رب اغفر لنا زلاتنا. يا رب افتقد مرضى شعبك، اشفهم من أجل اسمك القدوس. آباؤنا وإخوتنا الذين رقدوا، يا رب نيح نفوسهم. يا من هو بلا خطية، يا رب ارحمنا. يا من بلا خطية، يا رب أعنا، واقبل طلباتنا إليك. لأن لك المجد والعزة والتقديس المثلث. يا رب ارحم. يا رب ارحم يا رب بارك. آمين.",             "wight": "20"         }     ]</t>
-  </si>
-  <si>
-    <t>[         {             "question": "1-\t توجد ايقونة السيد المسيح علي الجانب الايسر من الباب الملوكي  ( x )",             "wight": "5"         },         {             "question": "2-\t في صحن الكنيسة يوجد باب واحد في الوسط  ( x )",             "wight": "5"         },         {             "question": "3-\t كلمة أوشية تعني محبة  ( x )",             "wight": "5"         },         {             "question": "4-\t يُصَلَّي قداس اللقان في الأعياد (عيد الغطاس – عيد الرسل – عيد خميس العهد – جميع ما سبق )   \n الاجابة : كل ما سبق",             "wight": "5"         },         {             "question": "5-\t يرمز بيت القربان إلي (بيت لحم – بيت صيدا – بيت مارمرقص )   \n الاجابة : بيت لحم",             "wight": "5"         },         {             "question": "6-\t السنكسار هو كتاب كنسي به (أعمال الرسل – سير القديسين – الأناجيل الأربعة )   \n الاجابة : سير القديسين",             "wight": "5"         },         {             "question": "7-  ماهو عدد القباب في الكنيسة ؟ \n1. إشارة إلى الرب يسوع \n2. إشارة إلى الثالوث القدوس \n3. إشارة إلى الرب حوله الإنجيليون الأربعة (متي، مرقس، لوقا ويوحنا).",             "wight": "12"         },         {             "question": "8-  إلي ماذا تشير الشورية؟ \nإلي ماما العذراء",             "wight": "2"         },         {             "question": "9-  إلي ماذا يشير  الجمر المُتقد ناراً؟ \nإلي جسد الرب يسوع",             "wight": "2"         },         {             "question": "10-  إلي ماذا يشير البخور؟ \n إلي بابا يسوع (مخلصنا)",             "wight": "2"         },         {             "question": "11-  إلي ماذا تشير الثلاث سلاسل ؟ \nإلي الثالوث القدوس (الآب والابن والروح القدس)",             "wight": "2"         },         {             "question": "12-   من أنواع الصلبان المستخدمة في الكنيسة .....صليب المذبح..... و ....صليب الدورة....",             "wight": "4"         },         {             "question": "13-  من الأدوات المستخدمة داخل الهيكل ....الكاس... و ....الماستير....",             "wight": "4"         },         {             "question": "14- يدهن الكاهن الشعب بالزيت بعد قراءة سفر ....الرؤيا.... في ليلة ابوغامسيس",             "wight": "2"         },         {             "question": "15-  سمع صلاة الشكر – الجزء الثاني: \n (أمَّاَ الصَّالِحاتُ والنَّافعاتُ فَارزُقْنا إيَّاهَا. لأنَّكَ أنْتَ الذِى أعْطَيتَنا السُّلْطانَ أنْ ندوسَ الحَيَّاتِ والعَقارِبَ وكُلَّ قوَّةِ العَدوِّ. ولا تُدْخِلنَا فى تَجربَةٍ، لَكنْ نَجِّنا مِنَ الشِّرِّيرِ. بالنِّعْمةِ والرَّأْفَاتِ ومَحبَّة البَشرِ اللَّواتِى لابنك الوَحيدِ ربِّنا وإلهِنَا ومُخلِّصِنا يَسُوعِ المسيحِ. هَذَا الذِى مِنْ قِبَلِه الَمجْدُ والإكْرام والعزَّةُ والسُّجودُ تَلِيقُ بكَ مَعهُ ومَعُ الرُّوحِ القُدُسِ المحيي المساوي لَكَ الآنَ وكلَّ أوَانٍ وإلىَ دَهرِ الدُّهُورِ. آمين).",             "wight": "8"         },         {             "question": "15-  سمع المزمور الخمسون كله: \n  ارحمني يا الله كعظيم رحمتك ، ومثل كثرة رأفآتك تمحو إثمي. اغسلني كثيرا من اثمي ومن خطيتي تطهرني ، لأني أنا عارف بإثمي وخطيتي امامي في كل حين ،  لك وحدك أخطأت، و الشر  قدامك صنعت. لكي تتبرر في اقوالك وتغلب إذا حوكمت . لأني هاأنذا بالإثم حبل بي ، و بالخطايا   ولدتني أمي. لأنك هكذا قد أحببت الحق،  إذ أوضحت لي غوامض حكمتك و مستوراتها ، تنضح على بزوفاك  فأطهر، تغسلني فأبيض أكثر من الثلج تسمعني سرورا وفرحا، فتبتهج عظامي المنسحقة. اصرف وجهك عن خطاياي، وامح كل آثامي. قلبا نقيا اخلق في يا الله، وروحا مستقيما جدده في أحشائي. لا تطرحني من قدام وجهك وروحك القدوس لا تنزعه منى. امنحني بهجة خلاصك ، وبروح رئاسي عضدني فأعلم الأثمة طرقك والمنافقون إليك يرجعون، نجني من الدماء يا الله إله خلاصي، فيبتهج لساني بعدلك. يا رب افتح شفتي ، فيخبر فمي بتسبيحك. لأنك لو آثرت الذبيحة لكنت الآن أعطي، ولكنك لا تسر بالمحرقات ، فالذبيحة لله روح منسحق. القلب المنكسر والمتواضع لا يرذله الله، أنعم يا رب بمسرتك على صهيون، ولتبن أسوار اورشليم حينئذ تسر بذبائح البر قربانا ومحرقات ويقربون على مذابحك التقدمات. هلليلويا",             "wight": "12"         }     ]</t>
-  </si>
-  <si>
-    <t>[         {             "question": "1-  اذكر ملابس الكاهن ) القس والقمص(: \n  ( التونية/ الشَمْلْة/ طيلسانة/ صَدْرَة )",             "wight": "16"         },         {             "question": "2- ما مدة صيام الميلاد  \n 43 يوم",             "wight": "4"         },         {             "question": "3- ولما تشير هذه المدة \n 40 يوم صيام موسى على الجبل، 3 أيام صيام نقل جبل المقطم",             "wight": "10"         },         {          "question": "4- اذكر ثلاثة من الأعياد السيدية الكبرى وثلاثة من الأعياد السيدية الصغرى\n الأعياد السيدية الكبرى \n1- عيد البشارة\n1 عيد الميلاد\n2 عيد الغطاس\n2- أحد الشعانين\n3- عيد القيامة \n5 عيد الصعود \n6 عيد العنصرة \nالأعياد السيدية الصغري\n1 -عيد الختان\n1-عرس قانا الجليل \n2-دخول المسيح الهيكل \n4-خميس العهد\n5-أحد توما\n6-دخول المسيح ارض مصر\n7-عيد التجلى",             "wight": "5"         },         {             "question": "5-  يوجد في الكنيسة القبطية ثلاث قداسات. أذكرهم واذكر من يخاطب كل قداس: \n قداس القديس مار مرقس الرسول ( القداس الكيرلسي ) يخاطب أقنوم الآب \n قداس القديس غريغوريوس الناطق بالإلهيات ( القداس الغريغوري ) يخاطب أقنوم الابن (السيد المَسيح) \n قداس القديس باسيليوس الكبير ( القداس الباسيلي ) يخاطب أقنوم الآب",             "wight": "12"         },         {             "question": "6- سمع : ارحمنا يا الله ثم ارحمنا. يا من في كل وقت وكل ساعة، في السماء وعلى الأرض، مسجود له وممجد. المسيح إلهنا الصالح، الطويل الروح، الكثير الرحمة، الجزيل التحنن، الذي يحب الصديقين ويرحم الخطاة الذين أولهم أنا. الذي لا يشاء موت الخاطئ مثل ما يرجع ويحيا. الداعي الكل إلى الخلاص لأجل الموعد بالخيرات المُنْتَظَرَة. يا رب اقبل منا في هذه الساعة وكل ساعة طلباتنا. سهل حياتنا، وأرشدنا إلى العمل بوصاياك. قدس أرواحنا. طهر أجسامنا. قوم أفكارنا. نق نياتنا. اشف أمراضنا واغفر خطايانا. ونجنا من كل حزن رديء ووجع قلب. أحطنا بملائكتك القديسين، لكي نكون بمعسكرهم محفوظين ومُرْشَدِين، لنصل إلى اتحاد الإيمان وإلى معرفة مجدك غير المحسوس وغير المحدود، فإنك مبارك إلى الأبد. آمين.",             "wight": "20"         }     ]</t>
-  </si>
-  <si>
     <t>coptic</t>
   </si>
   <si>
@@ -90,7 +81,11 @@
     <t>[         {             "question": "1-\tأوشية الزروع (عربي) - عشية وباكر وقداس\n(10 درجات عشية وباكر + 10 درجات قداس)",             "wight": "20"         },         {             "question": "2- أوشية أهوية السماء (عربي) - عشية وباكر وقداس\n(10 درجات عشية وباكر + 10 درجات قداس).",             "wight": "20"         },         {             "question": "3- أوشية المياة (عربي) - عشية وباكر وقداس\n(10 درجات عشية وباكر + 10 درجات قداس) ",             "wight": "20"         },         {             "question": "4-  آمين(3) طون ثاناطون  ",             "wight": "20"         },         {             "question": "5-\t تين هوس إيه روك (قبطي وعربي)\n( 10 درجات قبطي +  10 درجات عربي)",             "wight": "20"         },         {             "question": "6-\t كاطاطو إيه ليه أوس",             "wight": "10"         },         {             "question": "7-\t إيريه بو إسمو إثؤواب",             "wight": "15"         },         {             "question": "8-\t القارئون فليقولوا (قبطى وعربى)\n( 10 درجات قبطي +  10 درجات عربي)",             "wight": "20"         },         {             "question": "9-\t خلُصت حقاً ومع روحك (قبطى وعربى)\n( 10 درجات قبطي +  5  درجات عربي)",             "wight": "15"         },         {             "question": "10-\t الإعتراف الصغير (قبطي)",             "wight": "20"         }     ]</t>
   </si>
   <si>
-    <t>[{
+    <t>[
+        {
+            "instructions": "في حالة وجود أي استفسار يُرجَي الرجوع لخدام المادة:+أ/ بيشوي رضا حبيب: 01014222315 + أ/ إسحق إبراهيم: 01220068681"
+        },
+        {
             "question": "1-\tفى الكنيسة (نصلى) و (نرنم) و (نتعلم)",
             "wight": "2"
         },
@@ -123,43 +118,43 @@
             "wight": "2"
         },
         {
-            "question": "&lt;div style='text-align: center'&gt;&lt;span&gt;السؤال&lt;/span&gt;&lt;br&gt;&lt;img src='/admin/images/taks/1.jpg' &gt;&lt;/div&gt;",
+            "question": "&lt;div&gt;&lt;span&gt;9-\t    &lt;/span&gt;&lt;img src='/admin/images/taks/01(1).jpg' &gt;&lt;/div&gt;",
             "wight": "1"
         },
         {
-            "question": "10-\tسوال الصور  ",
+            "question": "&lt;div&gt;&lt;span&gt;10-\t    &lt;/span&gt;&lt;img src='/admin/images/taks/01(2).jpg' &gt;&lt;/div&gt;",
             "wight": "1"
         },
         {
-            "question": "11-\tسوال الصور  ",
+            "question": "&lt;div&gt;&lt;span&gt;11-\t    &lt;/span&gt;&lt;img src='/admin/images/taks/01(3).jpg' &gt;&lt;/div&gt;",
             "wight": "1"
         },
         {
-            "question": "12-\tسوال الصور  ",
+            "question": "&lt;div&gt;&lt;span&gt;12-\t    &lt;/span&gt;&lt;img src='/admin/images/taks/01(4).jpg' &gt;&lt;/div&gt;",
             "wight": "1"
         },
         {
-            "question": "13-\tسوال الصور  ",
+            "question": "&lt;div&gt;&lt;span&gt;13-\t    &lt;/span&gt;&lt;img src='/admin/images/taks/01(5).jpg' &gt;&lt;/div&gt;",
             "wight": "1"
         },
         {
-            "question": "14-\tسوال الصور  ",
+            "question": "&lt;div&gt;&lt;span&gt;14-\t    &lt;/span&gt;&lt;img src='/admin/images/taks/01(6).jpg' &gt;&lt;/div&gt;",
             "wight": "1"
         },
         {
-            "question": "15-\tسوال الصور  ",
+            "question": "&lt;div&gt;&lt;span&gt;15-\t    &lt;/span&gt;&lt;img src='/admin/images/taks/01(7).jpg' &gt;&lt;/div&gt;",
             "wight": "1"
         },
         {
-            "question": "16-\tسوال الصور  ",
+            "question": "&lt;div&gt;&lt;span&gt;16-\t    &lt;/span&gt;&lt;img src='/admin/images/taks/01(8).jpg' &gt;&lt;/div&gt;",
             "wight": "1"
         },
         {
-            "question": "17-\tسوال الصور  ",
+            "question": "&lt;div&gt;&lt;span&gt;17-\t    &lt;/span&gt;&lt;img src='/admin/images/taks/01(9).jpg' &gt;&lt;/div&gt;",
             "wight": "1"
         },
         {
-            "question": "18-\tسوال الصور  ",
+            "question": "&lt;div&gt;&lt;span&gt;18-\t    &lt;/span&gt;&lt;img src='/admin/images/taks/01(10).jpg' &gt;&lt;/div&gt;",
             "wight": "1"
         },
         {
@@ -167,8 +162,189 @@
             "wight": "10"
         },
         {
-            "question": "20-\tأبانا الذى فى السموات (بالقبطي) - الجزء الاول إلى (نان إيـﭭـول)",
+            "question": "17-\tأبانا الذى فى السموات (بالقبطي) - الجزء الاول إلى (نان إيـﭭـول)",
             "wight": "15"
+        }
+    ]</t>
+  </si>
+  <si>
+    <t>[
+        {
+            "instructions": "في حالة وجود أي استفسار يُرجَي الرجوع لخدام المادة:+أ/ بيشوي رضا حبيب 01014222315+أ/ إسحق إبراهيم 01220068681+أ/ چون عاطف 01284300589 "
+        },
+        {
+            "question": "1-\tعدد أسرار الكنيسة ( 4 – 5 – ..7.. )",
+            "wight": "2"
+        },
+        {
+            "question": "2-\tفي سر ( المعمودية – التناول – ..الزيجة.. ) يجمع فية ربنا اثنين ويوحدهم فى جسد واحد",
+            "wight": "2"
+        },
+        {
+            "question": "3-\tفى سر الميرون بنترشم  (33– 26 – ..36..)",
+            "wight": "2"
+        },
+        {
+            "question": "4-\tفي سر الكهنوت بيجي ........ ( الشماس – أبونا – ..المطران.. ) بيرشم إنسان ",
+            "wight": "2"
+        },
+        {
+            "question": "5-\tفي سر التوبة والاعتراف بنروح ........ ( لبابا – ماما – ..أبونا.. ) نعترف  بخطايانا",
+            "wight": "2"
+        },
+        {
+            "question": "6-\tسر التناول اسمه كمان سر ........... ( ..الشركة.. - الاعتراف – الزيجة )",
+            "wight": "2"
+        },
+        {
+            "question": "7-\tسر مسحة المرضة هو السر ........... ( الثاني – ..السابع.. – الخامس )",
+            "wight": "2"
+        },
+        {
+            "question": "8-\tاذكر أربعة من أسرار الكنيسة ؟\t\tالمعمودية – الميرون - التوبة والاعتراف – التناول - مسحة المرضي – الزيجة - الكهنوت",
+            "wight": "8"
+        },
+        {
+            "question": "9-\tتسميع السلام لك نسالك",
+            "wight": "15"
+        },
+        {
+            "question": "10-\tتسميع نعظمك يا ام النور الحقيقى",
+            "wight": "10"
+        }
+    ]</t>
+  </si>
+  <si>
+    <t>[
+        {
+            "instructions": "في حالة وجود أي استفسار يُرجَي الرجوع لخدام المادة:+أ/ چون عاطف 01284300589+أ/ ﭼون مجدي 01275034174 +أ/ ماركو ماهر 01221554457  "
+        },
+        {
+            "question": "1-\t ..يكون لون ستر الهيكل فى أسبوع الآلام   ..أسود..    وفى الخماسين    ..أبيض..   أما فى باقى الأيام ..أحمر",
+            "wight": "3"
+        },
+        {
+            "question": "2-\t  ..يعتبر أقدم بيت يجمع بين الله والإنسان هو  ..الفردوس",
+            "wight": "3"
+        },
+        {
+            "question": "3-\t\t...يفصل بين الهيكل والخورس    ...حامل الأيقونات",
+            "wight": "3"
+        },
+        {
+            "question": "4-\t .....أول كنيسة فى العالم كله هى بيت ......القديسة مريم والدة القديس مارمرقس ( العلية )",
+            "wight": "3"
+        },
+        {
+            "question": "5-  \t..إذا ما وقفنا فى هيكلك المقدس نُحسب كالقيام فى ..السماء ",
+            "wight": "3"
+        },
+        {
+            "question": "6- \tتُبْنَى الكنيسة حالياً على شكل سفينة\t(سفينة بطرس – ..فلك نوح.. – كل ماسبق)",
+            "wight": "3"
+        },
+        {
+            "question": "7-\t\tأغطية المذبح عددهم\t(اثنان – ..ثلاثة.. – خامسة)",
+            "wight": "3"
+        },
+        {
+            "question": "8- \tيوجد بالقسم الداخلي للكنيسة\t( الهيكل – الخورس – ..كل ماسبق..)",
+            "wight": "3"
+        },
+        {
+            "question": "9- \tداخل الهيكل نرى (دولاب الدياكونية – الدَرَج – الشرقية – المذبح – ..كل ما سبق..)",
+            "wight": "3"
+        },
+        {
+            "question": "10-    وظيفته حماية الكأس لئلا ينسكب\t(المستير – ..كرسي الكأس.. – المذبح)",
+            "wight": "3"
+        },
+        {
+            "question": "11-\tما هى الأشكال التي تُبْنَى عليها الكنيسة ؟ \t\tشكل السفينة      شكل الصليب       شكل الدائرة",
+            "wight": "4"
+        },
+        {
+            "question": "12-    ما هى أقسام الكنيسة من الداخل ؟\t\t\t     صحن الكنيسة        الخورس     الهيكل",
+            "wight": "4"
+        },
+        {
+            "question": "13-  \tلماذا ننظر ناحية الشرق فى صلواتنا؟\t\t     السيد المسيح صُلِبَ ناحية الشرق وسيأتى من الشرق",
+            "wight": "4"
+        },
+        {
+            "question": "14-  \tاذكر 5 أنواع من اللفائف في الكنيسة ؟\t\tلفافة الصنية - لفافة الحمل - لفافة الكاس - لفافة الكرسى – لفائف فرش المذبح - لفافة دورة الحمل - لفائف التناول",
+            "wight": "4"
+        },
+        {
+            "question": "15-    اذكر 5 من أدوات وأواني المذبح ؟\t              اللفائف – الصينية – الكأس – كرسى الكأس – المستير – القارورة – النجم - البشارة – درج البخور – الصليب",
+            "wight": "4"
+        },
+        {
+            "question": "16-\tتسميع قدوس، قدوس، قدوس، رب الصباؤوت",
+            "wight": "15"
+        },
+        {
+            "question": "17-\tتسميع فلنشكر صانع الخيرات إلي وعن موضعك المقدس هذا",
+            "wight": "10"
+        }
+    ]</t>
+  </si>
+  <si>
+    <t>[
+        {
+            "instructions": "في حالة وجود أي استفسار يُرجَي الرجوع لخدام المادة:+أ/ ﭼون مجدي 01275034174+أ/ ماركو ماهر 01221554457   "
+        },
+        {
+            "question": "1-\t مؤسس كل الأسرار هم التلاميذ وسلموها إلى من بعدهم  ( صح - ..خطأ..)",
+            "wight": "2"
+        },
+        {
+            "question": "2-\t يسمى سر الإفخارستيا بسر التناول وسر الأسرار  ( ..صح.. - خطأ)",
+            "wight": "2"
+        },
+        {
+            "question": "3-\t يتكون سر مسحة المرضى من 7 صلوات  ( ..صح.. - خطأ)",
+            "wight": "2"
+        },
+        {
+            "question": "4-\t سر الاعتراف لا يوجد له زمن أو ميعاد محدد  ( ..صح.. - خطأ)",
+            "wight": "2"
+        },
+        {
+            "question": "5-\t سر المعمودية له المرتبة الثانية بعد الكهنوت لأنه باب يدخل منه المؤمن إلى الكنيسة وملكوت النعمة  ( صح - ..خطأ..)",
+            "wight": "2"
+        },
+        {
+            "question": "6-\tمن إشارات المعمودية فى العهد القديم\t(..الطوفان.. – شجرة الحياة – لوحى الشريعة – مزامير داود)",
+            "wight": "4"
+        },
+        {
+            "question": "7-\tعدد رشومات زيت الميرون\t\t(37 رشمة – 140 رشمة – ..36 رشمة.. – 159 رشمة)",
+            "wight": "4"
+        },
+        {
+            "question": "8-\tالقناديل فى سر مسحة المرضى تكون\t(شمع – بخور - ..قطن..)",
+            "wight": "4"
+        },
+        {
+            "question": "9-\tأحضر زيت الميرون إلى مصر (البابا أثناسيوس الرسولى – البابا كيرلس عمود الدين – ..مار مرقس الرسول..)",
+            "wight": "4"
+        },
+        {
+            "question": "10- فى طقس الإكليل يوضع الإكليل على رأس (..الرجل والمرأة.. – المرأة فقط – الرجل فقط)",
+            "wight": "4"
+        },
+        {
+            "question": "11-\t  اشفوا مرضى ، طهروا برصاً ...  او  أية مدينة دخلتموها وقبلوكم .. فاشفوا المرضى الذين فيها  او أمريض أحد بينكم فليدع قسوس الكنيسة فيصلوا عليه ويدهنوه بزيت باسم الرب    --اذكر مما حفظت آية لسر مسحة المرضى؟ ",
+            "wight": "10"
+        },
+        {
+            "question": "12-    عَرِّف ماهو السر الكنسى؟   هو نعمة غير منظورة نحصل عليها بممارسة طقس منظور على يد كاهن شرعي بفعل الروح القدس",
+            "wight": "10"
+        },
+        {
+            "question": "13-  \tتسميع قانون الايمان",
+            "wight": "25"
         }
     ]</t>
   </si>
@@ -624,7 +800,7 @@
         <v>3</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C2">
         <v>1</v>
@@ -638,7 +814,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C3">
         <v>2</v>
@@ -652,7 +828,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="C4">
         <v>3</v>
@@ -666,7 +842,7 @@
         <v>3</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="C5">
         <v>4</v>
@@ -680,7 +856,7 @@
         <v>3</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="C6">
         <v>5</v>
@@ -694,7 +870,7 @@
         <v>3</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="C7">
         <v>6</v>
@@ -708,7 +884,7 @@
         <v>3</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="C8">
         <v>7</v>
@@ -722,7 +898,7 @@
         <v>3</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="C9">
         <v>8</v>
@@ -733,10 +909,10 @@
     </row>
     <row r="10" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C10">
         <v>1</v>
@@ -744,10 +920,10 @@
     </row>
     <row r="11" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C11">
         <v>2</v>
@@ -755,10 +931,10 @@
     </row>
     <row r="12" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C12">
         <v>3</v>
@@ -766,10 +942,10 @@
     </row>
     <row r="13" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C13">
         <v>4</v>
@@ -777,10 +953,10 @@
     </row>
     <row r="14" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
+        <v>4</v>
+      </c>
+      <c r="B14" s="1" t="s">
         <v>7</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>10</v>
       </c>
       <c r="C14">
         <v>5</v>
@@ -788,10 +964,10 @@
     </row>
     <row r="15" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C15">
         <v>6</v>
@@ -799,10 +975,10 @@
     </row>
     <row r="16" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C16">
         <v>7</v>
@@ -810,10 +986,10 @@
     </row>
     <row r="17" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C17">
         <v>8</v>
@@ -821,10 +997,10 @@
     </row>
     <row r="18" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C18">
         <v>1</v>
@@ -832,10 +1008,10 @@
     </row>
     <row r="19" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C19">
         <v>2</v>
@@ -843,10 +1019,10 @@
     </row>
     <row r="20" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
+        <v>10</v>
+      </c>
+      <c r="B20" s="1" t="s">
         <v>13</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>16</v>
       </c>
       <c r="C20">
         <v>3</v>
@@ -854,10 +1030,10 @@
     </row>
     <row r="21" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C21">
         <v>4</v>
@@ -865,10 +1041,10 @@
     </row>
     <row r="22" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C22">
         <v>5</v>
@@ -876,10 +1052,10 @@
     </row>
     <row r="23" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C23">
         <v>6</v>
@@ -887,10 +1063,10 @@
     </row>
     <row r="24" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C24">
         <v>7</v>
@@ -898,10 +1074,10 @@
     </row>
     <row r="25" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C25">
         <v>8</v>

--- a/exams_import.xlsx
+++ b/exams_import.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\MY_WORK\peter\qr-exams-system\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E627841-D79E-432A-9439-00245335C4E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96510547-23EA-4CBA-9C3C-2D4C0CCA1E03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5760" yWindow="2268" windowWidth="17280" windowHeight="8964" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="0" iterateDelta="1E-4"/>
   <extLst>
@@ -25,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="22">
   <si>
     <t>type</t>
   </si>
@@ -1087,4 +1088,289 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AEAA58B4-CCC6-449D-B1B2-34A66B80EAA5}">
+  <dimension ref="A1:C25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C7">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C8">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>3</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C9">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>4</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C11">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>4</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C12">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>4</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C13">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>4</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C14">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>4</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C15">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>4</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>4</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C17">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>10</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>10</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C19">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>10</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C20">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>10</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C21">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>10</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C22">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>10</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C23">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>10</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C24">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>10</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C25">
+        <v>8</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/exams_import.xlsx
+++ b/exams_import.xlsx
@@ -1,23 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26924"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27029"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\MY_WORK\peter\qr-exams-system\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96510547-23EA-4CBA-9C3C-2D4C0CCA1E03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F0E4E87-201E-4AC3-B9B6-E9ED99560508}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="11520" windowHeight="12360" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="0" iterateDelta="1E-4"/>
+  <calcPr calcId="191029"/>
   <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
     </ext>
@@ -26,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="59">
   <si>
     <t>type</t>
   </si>
@@ -346,6 +357,1418 @@
         {
             "question": "13-  \tتسميع قانون الايمان",
             "wight": "25"
+        }
+    ]</t>
+  </si>
+  <si>
+    <t>[
+        {
+            "instructions": "في حالة وجود أي استفسار يُرجَي الرجوع لخدام المادة:+أ/ بيشوي رضا حبيب: 01014222315 + أ/ إسحق إبراهيم: 01220068681"
+        },
+        {
+            "question": "1-\t.........فى الكنيسة....... و ......... و ",
+            "wight": "2",
+            "ans": "فى الكنيسة (نصلى) و (نرنم) و (نتعلم)"
+        },
+        {
+            "question": "2- ......فرحت   ......  لى إلى  ...... الرب",
+            "wight": "2",
+            "ans": "فرحت   (بالقائلين)  لى إلى  (بيت)  الرب  (نذهب)"
+        },
+        {
+            "question": "3- .......أما أنا  .....  رحمتك  .....  بيتك و .....  قدام  ....... قدسك ",
+            "wight": "2",
+            "ans": "أما أنا  (فبكثرة)  رحمتك  (أدخل)  بيتك و (أسجد)  قدام  (هيكل)  قدسك  (بمخافتك)"
+        },
+        {
+            "question": "4- ..........فى الكنيسة بنشوف أيقونات .......   و.......  و   ",
+            "wight": "2",
+            "ans": "فى الكنيسة بنشوف أيقونات (بابا يسوع)   و(ماما العذراء)  و  (القديسين والقديسات)"
+        },
+        {
+            "question": "5-\t ........الكنيسة هى بيتنا كلنا وبيت ....... و ",
+            "wight": "2",
+            "ans": "الكنيسة هى بيتنا كلنا وبيت (الملائكة) و (القديسين)"
+        },
+        {
+            "question": "6-\t  ........مساكنك .....  أيها الرب  إله  ",
+            "wight": "2",
+            "ans": "مساكنك (محبوبة)  أيها الرب  إله (القوات)"
+        },
+        {
+            "question": "7-\t  .......لما بشوف الصينية والنجمة بافتكر",
+            "wight": "2",
+            "ans": "لما بشوف الصينية والنجمة بافتكر (المذود)"
+        },
+        {
+            "question": "8-\t ........الشورية بتفكرنا لما كان بابا يسوع فى ",
+            "wight": "2",
+            "ans": "الشورية بتفكرنا لما كان بابا يسوع فى  (بطن ماما العذراء)"
+        },
+        {
+            "question": "&lt;div&gt;&lt;span&gt;9-\t    &lt;/span&gt;&lt;img src='/admin/images/taks/01(1).jpg' &gt;&lt;/div&gt;",
+            "ans": "الكرسي",
+            "wight": "1"
+        },
+        {
+            "question": "&lt;div&gt;&lt;span&gt;10-\t    &lt;/span&gt;&lt;img src='/admin/images/taks/01(2).jpg' &gt;&lt;/div&gt;",
+            "ans": "المستير",
+            "wight": "1"
+        },
+        {
+            "question": "&lt;div&gt;&lt;span&gt;11-\t    &lt;/span&gt;&lt;img src='/admin/images/taks/01(3).jpg' &gt;&lt;/div&gt;",
+            "ans": "المنجلية",
+            "wight": "1"
+        },
+        {
+            "question": "&lt;div&gt;&lt;span&gt;12-\t    &lt;/span&gt;&lt;img src='/admin/images/taks/01(4).jpg' &gt;&lt;/div&gt;",
+            "ans": "الكأس",
+            "wight": "1"
+        },
+        {
+            "question": "&lt;div&gt;&lt;span&gt;13-\t    &lt;/span&gt;&lt;img src='/admin/images/taks/01(5).jpg' &gt;&lt;/div&gt;",
+            "ans": "اللفافة",
+            "wight": "1"
+        },
+        {
+            "question": "&lt;div&gt;&lt;span&gt;14-\t    &lt;/span&gt;&lt;img src='/admin/images/taks/01(6).jpg' &gt;&lt;/div&gt;",
+            "ans": "القبة",
+            "wight": "1"
+        },
+        {
+            "question": "&lt;div&gt;&lt;span&gt;15-\t    &lt;/span&gt;&lt;img src='/admin/images/taks/01(7).jpg' &gt;&lt;/div&gt;",
+            "ans": "الصينية",
+            "wight": "1"
+        },
+        {
+            "question": "&lt;div&gt;&lt;span&gt;16-\t    &lt;/span&gt;&lt;img src='/admin/images/taks/01(8).jpg' &gt;&lt;/div&gt;",
+            "ans": "الشورية",
+            "wight": "1"
+        },
+        {
+            "question": "&lt;div&gt;&lt;span&gt;17-\t    &lt;/span&gt;&lt;img src='/admin/images/taks/01(9).jpg' &gt;&lt;/div&gt;",
+            "ans": "الأيقونات",
+            "wight": "1"
+        },
+        {
+            "question": "&lt;div&gt;&lt;span&gt;18-\t    &lt;/span&gt;&lt;img src='/admin/images/taks/01(10).jpg' &gt;&lt;/div&gt;",
+            "ans": "المذبح",
+            "wight": "1"
+        }
+    ]</t>
+  </si>
+  <si>
+    <t>[
+        {
+            "instructions": "في حالة وجود أي استفسار يُرجَي الرجوع لخدام المادة:+أ/ بيشوي رضا حبيب 01014222315+أ/ إسحق إبراهيم 01220068681+أ/ چون عاطف 01284300589 "
+        },
+        {
+            "question": "1-\tعدد أسرار الكنيسة ( 4 – 5 – 7 )",
+            "wight": "2",
+            "ans": "7"
+        },
+        {
+            "question": "2-\tفي سر ( المعمودية – التناول – الزيجة ) يجمع فية ربنا اثنين ويوحدهم فى جسد واحد",
+            "wight": "2",
+            "ans": "الزيجة"
+        },
+        {
+            "question": "3-\tفى سر الميرون بنترشم  (33– 26 – 36 )",
+            "wight": "2",
+            "ans": "36"
+        },
+        {
+            "question": "4-\tفي سر الكهنوت بيجي ........ ( الشماس – أبونا – المطران ) بيرشم إنسان ",
+            "wight": "2",
+            "ans": "المطران"
+        },
+        {
+            "question": "5-\tفي سر التوبة والاعتراف بنروح ........ ( لبابا – ماما – أبونا ) نعترف  بخطايانا",
+            "wight": "2",
+            "ans": "أبونا"
+        },
+        {
+            "question": "6-\tسر التناول اسمه كمان سر ........... ( الشركة - الاعتراف – الزيجة )",
+            "wight": "2",
+            "ans": "الشركة"
+        },
+        {
+            "question": "7-\tسر مسحة المرضة هو السر ........... ( الثاني – السابع – الخامس )",
+            "wight": "2",
+            "ans": "السابع"
+        },
+        {
+            "question": "8-\tاذكر أربعة من أسرار الكنيسة ؟",
+            "wight": "8",
+            "ans": "المعمودية – الميرون - التوبة والاعتراف – التناول - مسحة المرضي – الزيجة - الكهنوت"
+        }
+    ]</t>
+  </si>
+  <si>
+    <t>[
+        {
+            "instructions": "في حالة وجود أي استفسار يُرجَي الرجوع لخدام المادة:+أ/ چون عاطف 01284300589+أ/ ﭼون مجدي 01275034174 +أ/ ماركو ماهر 01221554457  "
+        },
+        {
+            "question": "1-\t .........يكون لون ستر الهيكل فى أسبوع الآلام   ......... وفى الخماسين........أما فى باقى الأيام",
+            "wight": "3",
+            "ans": "..يكون لون ستر الهيكل فى أسبوع الآلام   ..أسود..    وفى الخماسين    ..أبيض..   أما فى باقى الأيام ..أحمر"
+        },
+        {
+            "question": "2-\t .........يعتبر أقدم بيت يجمع بين الله والإنسان هو",
+            "wight": "3",
+            "ans": "..يعتبر أقدم بيت يجمع بين الله والإنسان هو  ..الفردوس"
+        },
+        {
+            "question": "3-\t\t......يفصل بين الهيكل والخورس",
+            "wight": "3",
+            "ans": "...يفصل بين الهيكل والخورس...حامل الأيقونات"
+        },
+        {
+            "question": "4-\t .................أول كنيسة فى العالم كله هى بيت",
+            "wight": "3",
+            "ans": "أول كنيسة فى العالم كله هى بيت ......القديسة مريم والدة القديس مارمرقس ( العلية )"
+        },
+        {
+            "question": "5-  \t........إذا ما وقفنا فى هيكلك المقدس نُحسب كالقيام فى",
+            "wight": "3",
+            "ans": "..إذا ما وقفنا فى هيكلك المقدس نُحسب كالقيام فى ..السماء "
+        },
+        {
+            "question": "6- \tتُبْنَى الكنيسة حالياً على شكل سفينة\t(سفينة بطرس – فلك نوح – كل ماسبق)",
+            "wight": "3",
+            "ans": "فلك نوح"
+        },
+        {
+            "question": "7-\t\tأغطية المذبح عددهم\t(اثنان – ثلاثة – خامسة)",
+            "wight": "3",
+            "ans": "ثلاثة"
+        },
+        {
+            "question": "8- \tيوجد بالقسم الداخلي للكنيسة\t( الهيكل – الخورس – كل ماسبق)",
+            "wight": "3",
+            "ans": "كل ماسبق"
+        },
+        {
+            "question": "9- \tداخل الهيكل نرى (دولاب الدياكونية – الدَرَج – الشرقية – المذبح – كل ماسبق)",
+            "wight": "3",
+            "ans": "كل ماسبق"
+        },
+        {
+            "question": "10-    وظيفته حماية الكأس لئلا ينسكب\t(المستير – كرسي الكأس – المذبح)",
+            "wight": "3",
+            "ans": "كرسي الكأس"
+        },
+        {
+            "question": "11-\tما هى الأشكال التي تُبْنَى عليها الكنيسة ؟",
+            "wight": "4",
+            "ans": "شكل السفينة - شكل الصليب - شكل الدائرة"
+        },
+        {
+            "question": "12-ما هى أقسام الكنيسة من الداخل ؟",
+            "wight": "4",
+            "ans": "صحن الكنيسة - الخورس - الهيكل"
+        },
+        {
+            "question": "13-\tلماذا ننظر ناحية الشرق فى صلواتنا؟",
+            "wight": "4",
+            "ans": "السيد المسيح صُلِبَ ناحية الشرق وسيأتى من الشرق"
+        },
+        {
+            "question": "14-\tاذكر 5 أنواع من اللفائف في الكنيسة ؟",
+            "wight": "4",
+            "ans": "لفافة الصنية - لفافة الحمل - لفافة الكاس - لفافة الكرسى – لفائف فرش المذبح - لفافة دورة الحمل - لفائف التناول"
+        },
+        {
+            "question": "15-    اذكر 5 من أدوات وأواني المذبح ؟",
+            "wight": "4",
+            "ans": " اللفائف – الصينية – الكأس – كرسى الكأس – المستير – القارورة – النجم - البشارة – درج البخور – الصليب"
+        }
+    ]</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> [
+        {
+            "instructions": "في حالة وجود أي استفسار يُرجَي الرجوع لخدام المادة:+أ/ ﭼون مجدي 01275034174+أ/ ماركو ماهر 01221554457   "
+        },
+        {
+            "question": "1-\t مؤسس كل الأسرار هم التلاميذ وسلموها إلى من بعدهم  ( صح - خطأ)",
+            "wight": "2",
+            "ans": "خطأ"
+        },
+        {
+            "question": "2-\t يسمى سر الإفخارستيا بسر التناول وسر الأسرار  ( صح - خطأ)",
+            "wight": "2",
+            "ans": "صح"
+        },
+        {
+            "question": "3-\t يتكون سر مسحة المرضى من 7 صلوات  ( صح - خطأ)",
+            "wight": "2",
+            "ans": "صح"
+        },
+        {
+            "question": "4-\t سر الاعتراف لا يوجد له زمن أو ميعاد محدد  ( صح - خطأ)",
+            "wight": "2",
+            "ans": "صح"
+        },
+        {
+            "question": "5-\t سر المعمودية له المرتبة الثانية بعد الكهنوت لأنه باب يدخل منه المؤمن إلى الكنيسة وملكوت النعمة  ( صح - خطأ)",
+            "wight": "2",
+            "ans": "خطأ"
+        },
+        {
+            "question": "6-\tمن إشارات المعمودية فى العهد القديم\t(الطوفان – شجرة الحياة – لوحى الشريعة – مزامير داود)",
+            "wight": "4",
+            "ans": "الطوفان"
+        },
+        {
+            "question": "7-\tعدد رشومات زيت الميرون\t\t(37 رشمة – 140 رشمة – 36 رشمة – 159 رشمة)",
+            "wight": "4",
+            "ans": "36 رشمة"
+        },
+        {
+            "question": "8-\tالقناديل فى سر مسحة المرضى تكون\t(شمع – بخور -قطن)",
+            "wight": "4",
+            "ans": "قطن"
+        },
+        {
+            "question": "9-\tأحضر زيت الميرون إلى مصر (البابا أثناسيوس الرسولى – البابا كيرلس عمود الدين – مار مرقس الرسول)",
+            "wight": "4",
+            "ans": "مار مرقس الرسول"
+        },
+        {
+            "question": "10- فى طقس الإكليل يوضع الإكليل على رأس (الرجل والمرأة – المرأة فقط – الرجل فقط)",
+            "wight": "4",
+            "ans": "الرجل والمرأة"
+        },
+        {
+            "question": "11-\tاذكر مما حفظت آية لسر مسحة المرضى؟ ",
+            "wight": "10",
+            "ans": "اشفوا مرضى ، طهروا برصاً ...  او  أية مدينة دخلتموها وقبلوكم .. فاشفوا المرضى الذين فيها  او أمريض أحد بينكم فليدع قسوس الكنيسة فيصلوا عليه ويدهنوه بزيت باسم الرب"
+        },
+        {
+            "question": "12- عَرِّف ماهو السر الكنسى؟",
+            "wight": "10",
+            "ans": "هو نعمة غير منظورة نحصل عليها بممارسة طقس منظور على يد كاهن شرعي بفعل الروح القدس"
+        }
+    ]</t>
+  </si>
+  <si>
+    <t>agbeya</t>
+  </si>
+  <si>
+    <t>[
+        {
+            "instructions": "في حالة وجود أي استفسار يُرجَي الرجوع لخدام المادة:+أ/ بيشوي رضا حبيب: 01014222315 + أ/ إسحق إبراهيم: 01220068681"
+        },
+        {
+            "question": "1-\tأبانا الذى فى السموات (بالقبطي) - الجزء الاول إلى (نان إيـﭭـول)",
+            "wight": "15",
+            "answer": "آريتين انئمبشا انجوس  خين أو شبئهموت جى بينيوت اتخين نيفيؤى مارى يوفطوفو انجى بيكران. مار يسئى انجى تيكميتئورو. بيتيهناك مار يف شوبى إم افريتى خين اتفى نيم هيجين بى كاهى بين أويك انتى راستى ميف نان امفوؤو أووه كانيئتيرون نان إيفول"
+        },
+        {
+            "question": "2-\tأبانا الذى فى السموات (بالعربي) ",
+            "wight": "10",
+            "ans": "أبانا الذي في السماوات. ليتقدس اسمك. ليأت ملكوتك. لتكن مشيئتك. كما في السماء كذلك على الأرض.خبزنا الذي للغد أعطنا اليوم.وأغفر لنا ذنوبنا كما نغفر نحن أيضا للمذنبين إلينا.ولا تدخلنا في تجربة. لكن نجنا من الشرير.بالمسيح يسوع ربنا لأن لك الملك والقوة والمجد إلى الأبد. آمين."
+        }
+    ]</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> [
+        {
+            "instructions": "في حالة وجود أي استفسار يُرجَي الرجوع لخدام المادة:+أ/ بيشوي رضا حبيب 01014222315+أ/ إسحق إبراهيم 01220068681+أ/ چون عاطف 01284300589 "
+        },
+        {
+            "question": "1-\tتسميع السلام لك نسالك",
+            "wight": "15",
+            "answer": "السلام لكي. نسألك أيتها القديسة الممتلئة مجدا العذراء كل حين، والدة الإله أم المسيح، أصْعِدي صلواتنا إلى ابنك الحبيب ليغفر لنا خطايانا. السلام للتي ولدت لنا النور الحقيقي المسيح إلهنا، العذراء القديسة، اسألي الرب عنا، ليصنع رحمة مع نفوسنا، ويغفر لنا خطايانا. أيتها العذراء مريم والدة الإله، القديسة الشفيعة الأمينة لجنس البشرية، اشفعي فينا أمام المسيح الذي ولدته لكي ينعم علينا بغفران خطايانا.السلام لك أيتها العذراء الملكة الحقيقية، السلام لفخر جنسنا، ولدت لنا عمانوئيل. نسألك: اذكرينا، أيتها الشفيعة المؤتمنة، أمام ربنا يسوع المسيح، ليغفر لنا خطايانا."
+        },
+        {
+            "question": "2-\tتسميع نعظمك يا ام النور الحقيقى",
+            "wight": "10",
+            "answer": "نعظمك يا أم النور الحقيقي ونمجدك أيتها العذراء القديسة, والدة الإله, لأنك ولدت لنا مخلص العالم, أتى وخلص نفوسنا.المجد لك يا سيدنا و ملكنا المسيح, فخر الرسل, إكليل الشهداء, تهليل الصديقين, ثبات الكنائس, غفران الخطايا.نبشر بالثالوث القدوس, لاهوت واحد, نسجد له و نمجده. يا رب أرحم. يا رب ارحم. يا رب بارك، آمين"
+        }
+    ]</t>
+  </si>
+  <si>
+    <t>[
+        {
+            "instructions": "في حالة وجود أي استفسار يُرجَي الرجوع لخدام المادة:+أ/ چون عاطف 01284300589+أ/ ﭼون مجدي 01275034174 +أ/ ماركو ماهر 01221554457  "
+        },
+        {
+            "question": "1-\tتسميع قدوس، قدوس، قدوس، رب الصباؤوت",
+            "wight": "15",
+            "answer": "قدوس، قدوس، قدوس، رب الصباؤوت. السماء والأرض مملوءتان من مجدك وكرامتك. ارحمنا يا الله الآب ضابط الكل. أيها الثالوث القدوس ارحمنا. أيها الرب إله القوات كن معنا، لأنه ليس لنا معين في شدائدنا وضيقاتنا سواك. حل واغفر واصفح لنا يا الله عن سيئاتنا، التي صنعناها بإرادتنا والتي صنعناها بغير إرادتنا، التي فعلناها بمعرفة والتي فعلناها بغير معرفة، الخفية والظاهرة. يا رب اغفرها لنا، من أجل اسمك القدوس الذي دعي علينا. كرحمتك يا رب وليس كخطايانا."
+        },
+        {
+            "question": "2-\tتسميع فلنشكر صانع الخيرات إلي وعن موضعك المقدس هذا",
+            "wight": "10",
+            "answer": "فلنشكر صانع الخيرات الرحوم الله، أبا ربنا وإلهنا ومخلصنا يسوع المسيح. لأنه سترنا وأعاننا، وحفظنا، وقبلنا إليه، وأشفق علينا، وعضدنا، وأتى بنا  إلى هذه الساعة. هو أيضًا فلنسأله أن يحفظنا في هذا اليوم المقدس وكل أيام  حياتنا بكل سلام، الضابط الكل الرب إلهنا. أيها السيد الرب الإله ضابط الكل أبو ربنا وإلهنا ومخلصنا يسوع المسيح، نشكرك على كل حال، ومن أجل كل حال، وفى كل حال، لأنك سترتنا وأعنتنا وحفظتنا وقبلتنا إليك، وأشفقت علينا وعضدتنا وأتيت بنا إلى هذه الساعة. من أجل هذا نسأل ونطلب من صلاحك يا محب البشر، امنحنا أن نكمل هذا اليوم  المقدس وكل أيام حياتنا بكل سلام مع خوفك. كل حسد وكل تجربة وكل فعل الشيطان  ومؤامرة الناس الأشرار، وقيام الأعداء الخفيين والظاهرين، انزعها عنا وعن  سائر شعبك وعن موضعك المقدس هذا. أما الصالحات والنافعات فارزقنا إياها، لأنك أنت الذي أعطيتنا السلطان أن ندوس الحيات والعقارب وكل قوة العدو ولا تدخلنا في تجربة، لكن نجنا من الشرير. بالنعمة والرأفات ومحبة البشر، اللواتي لابنك الوحيد ربنا وإلهنا ومخلصنا يسوع المسيح. هذا الذي من قبله  المجد والإكرام والعزة والسجود تليق بك معه ومع الروح القدس المحيى المساوي لك الآن وكل أوان وإلى دهر الدهور. آمين."
+        }
+    ]</t>
+  </si>
+  <si>
+    <t>[
+        {
+            "instructions": "في حالة وجود أي استفسار يُرجَي الرجوع لخدام المادة:+أ/ ﭼون مجدي 01275034174+أ/ ماركو ماهر 01221554457   "
+        },
+        {
+            "question": "1-  \tتسميع قانون الايمان",
+            "wight": "25",
+            "answer": "بالحقيقة نؤمن بإله واحد، الله الآب، ضابط الكل، خالق السماء و الأرض، ما يرى و ما لا يرى. نؤمن برب واحد يسوع المسيح، ابن الله الوحيد، المولود من الآب قبل كل الدهور، نور من نور، إله حق من إله حق، مولود غير مخلوق، مساو للآب في الجوهر، الذي به كان كل شيء. هذا الذي من أجلنا نحن البشر، و من أجل خلاصنا، نزل من السماء و تجسد من الروح القدس و من مريم العذراء. تأنس و صلب عنا على عهد بيلاطس البنطي. تألم و قبر و قام من بين الأموات في اليوم الثالث كما في الكتب، و صعد إلى السموات، و جلس عن يمين أبيه، وأيضًا يأتي في مجده ليدين الأحياء و الأموات، الذي ليس لملكه انقضاء.نعم نؤمن بالروح القدس، الرب المحيي المنبثق من الآب. نسجد له و نمجده مع الآب والابن، الناطق في الأنبياء. و بكنيسة واحدة مقدسة جامعة رسولية. و نعترف بمعمودية واحدة لمغفرة الخطايا. و ننتظر قيامة الأموات و حياة الدهر الآتي. آمين."
+        }
+    ]</t>
+  </si>
+  <si>
+    <t>[
+        {
+            "instructions": "في حالة وجود أي استفسار يُرجَي الرجوع لخدام المادة:  أ/ ميلاد ميخائيل: 01220068681"
+        },
+        {
+            "question": "1- هَلمَّ نسجد.",
+            "wight": "5",
+            "answer": "هلم نسجد هلم نسأل المسيح إلهنا. هلم نسجد، هلم نطلب من المسيح ملكنا. هلم نسجد، هلم نتضرع إلى المسيح مخلصنا. يا ربنا يسوع المسيح كلمة الله إلهنا، بشفاعة القديسة مريم وجميع قديسيك، احفظنا ولنبدأ بدءا حسنا. ارحمنا كإرادتك إلى الأبد. الليل عبر، نشكرك يا رب ونسأل أن تحفظنا في هذا اليوم بغير خطية وأنقذنا."
+        },
+        {
+            "question": "2- أسْألُكُم أنَا الأسير في الرب",
+            "wight": "5",
+            "answer": "أسألكم أنا الأسير في الرب أن تسلكوا كما يحق للدعوة التي دعيتم إليها، بكل تواضع القلب والوداعة وطول الأناة، محتملين بعضكم بعضا بالمحبة، مسرعين إلى حفظ وحدانية الروح برباط الصلح الكامل لكي تكونوا جسدًا واحدًا وروحًا واحدا، كما دعيتم في رجاء دعوتكم الواحد. ربٍّ واحد. وإيمان واحد. ومعمودية واحدة."
+        },
+        {
+            "question": "3- واحِدٌ هُوَ الله أبُو كلِّ أحَدٍ",
+            "wight": "5",
+            "answer": "واحد هو الله أبو كل أحد. واحد هو أيضا ابنه يسوع المسيح الكلمة، الذي تجسد ومات وقام من الأموات في اليوم الثالث وأقامنا معه، واحد هو الروح القدس المعزى الواحد بأقنومه، منبثق من الآب، يطهر كل البرية. يعلمنا أن نسجد للثالوث القدوس بلاهوت واحد وطبيعة واحدة، نسبحه ونباركه إلى الأبد. آمين."
+        },
+        {
+            "question": "4- مزمور يارَبَّ مَنْ يسكن فى مَسْكنِكَ",
+            "wight": "5",
+            "answer": "يا رب من يسكن في مسكنك، ومن يحل في جبل قدسك؟ السالك بلا عيب والفاعل البر، والمتكلم بالحق في قلبه، الذي لا يغش بلسانه، ولا يصنع بقريبه سوءا، ولا يقبل عارا على جيرانه. فاعل الشر مرذول أمامه، ويمجد الذين يتقون الرب. الذي يحلف لقريبه ولا يغدر به. ولا يعطى فضته بالربا، ولا يقبل الرشوة على الأبرياء. الذي يصنع هذا لا يتزعزع إلى الأبد. هلليلويا."
+        }
+    ]</t>
+  </si>
+  <si>
+    <t>[
+        {
+            "instructions": "في حالة وجود أي استفسار يُرجَي الرجوع لخدام المادة:  أ/ جورج عادل: 01220068681"
+        },
+        {
+            "question": "1- مزمور أعظِّمُكَ يا رَبُّ لأنَّكَ احتضنتني",
+            "wight": "5",
+            "answer": "أُعَظِّمُكَ يَا رَبُّ لأَنَّكَ نَشَلْتَنِي وَلَمْ تُشْمِتْ بِي أَعْدَائِي. يَا رَبُّ إِلهِي، اسْتَغَثْتُ بِكَ فَشَفَيْتَنِي. يَا رَبُّ، أَصْعَدْتَ مِنَ الْهَاوِيَةِ نَفْسِي. أَحْيَيْتَنِي مِنْ بَيْنِ الْهَابِطِينَ فِي الْجُبِّ. رَنِّمُوا لِلرَّبِّ يَا أَتْقِيَاءَهُ، وَاحْمَدُوا ذِكْرَ قُدْسِهِ. لأَنَّ لِلَحْظَةٍ غَضَبَهُ. حَيَاةٌ فِي رِضَاهُ. عِنْدَ الْمَسَاءِ يَبِيتُ الْبُكَاءُ، وَفِي الصَّبَاحِ تَرَنُّمٌ. وَأَنَا قُلْتُ فِي طُمَأْنِينَتِي: «لاَ أَتَزَعْزَعُ إِلَى الأَبَدِ». يَا رَبُّ، بِرِضَاكَ ثَبَّتَّ لِجَبَلِي عِزًّا. حَجَبْتَ وَجْهَكَ فَصِرْتُ مُرْتَاعًا. إِلَيْكَ يَا رَبُّ أَصْرُخُ، وإِلَى السَّيِّدِ أَتَضَرَّعُ مَا الْفَائِدَةُ مِنْ دَمِي إِذَا نَزَلْتُ إِلَى الْحُفْرَةِ؟ هَلْ يَحْمَدُكَ التُّرَابُ؟ هَلْ يُخْبِرُ بِحَقِّكَ؟ اسْتَمِعْ يَا رَبُّ وَارْحَمْنِي. يَا رَبُّ، كُنْ مُعِينًا لِي. حَوَّلْتَ نَوْحِي إِلَى رَقْصٍ لِي. حَلَلْتَ مِسْحِي وَمَنْطَقْتَنِي فَرَحًا، لِكَيْ تَتَرَنَّمَ لَكَ رُوحِي وَلاَ تَسْكُتَ. يَا رَبُّ إِلهِي، إِلَى الأَبَدِ أَحْمَدُكَ."
+        },
+        {
+            "question": "2- مزمور الرب يرعاني",
+            "wight": "5",
+            "answer": "الرَّبُّ رَاعِيَّ فَلاَ يُعْوِزُنِي شَيْءٌ. فِي مَرَاعٍ خُضْرٍ يُرْبِضُنِي. إِلَى مِيَاهِ الرَّاحَةِ يُورِدُنِي. يَرُدُّ نَفْسِي. يَهْدِينِي إِلَى سُبُلِ الْبِرِّ مِنْ أَجْلِ اسْمِهِ. أَيْضًا إِذَا سِرْتُ فِي وَادِي ظِلِّ الْمَوْتِ لاَ أَخَافُ شَرًّا، لأَنَّكَ أَنْتَ مَعِي. عَصَاكَ وَعُكَّازُكَ هُمَا يُعَزِّيَانِنِي. تُرَتِّبُ قُدَّامِي مَائِدَةً تُجَاهَ مُضَايِقِيَّ. مَسَحْتَ بِالدُّهْنِ رَأْسِي. كَأْسِي رَيَّا. إِنَّمَا خَيْرٌ وَرَحْمَةٌ يَتْبَعَانِنِي كُلَّ أَيَّامِ حَيَاتِي، وَأَسْكُنُ فِي بَيْتِ الرَّبِّ إِلَى مَدَى الأَيَّامِ."
+        },
+        {
+            "question": "3- إنجيل الساعة الثالثة",
+            "wight": "10",
+            "answer": "متى جاء المعزى الروح القدس الذي سيرسله الآب باسمي، فهو يعلمكم كل شيء ويذكركم بكل ما قلته لكم. سلامي أترك لكم. سلامي أنا أعطيكم. ليس كما يعطى العالمُ أعطيكم. لا تضطرب قلوبكم ولا تجزع. سمعتم أنى قلت لكم إني أمضى ثم آتى إليكم. لو كنتم تحبونني لكنتم تفرحون لأني أمضى إلى الآب، لأن أبى أعظمُ منى. وقد قلتُ لكم الآن قبل أن يكون، حتى متى كان تؤمنون. لست أكلمكم كلاما كثيرا بعد، لأن رئيس هذا العالم آتٍ وليس له في شيءٌ. لكن لكي يعلمَ العالمُ أنني أحب أبى، وكما أوصاني أبى هكذا أفعل، قوموا ننطلق من ههنا.أنا هو الكرمة الحقيقية وأبى الكرام. كل غصن فيّ لا يأتي بثمر يقطعه. وكل ما يأتي بثمر ينقيه ليأتي بثمر أكثر. وأنتم من قبْل أنقياءُ من أجل الكلام الذي كلمتكم به. اثبتوا في وأنا أيضا فيكم. (والمجد لله دائمًا)."
+        }
+    ]</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> [
+        {
+            "instructions": "في حالة وجود أي استفسار يُرجَي الرجوع لخدام المادة:  أ/ ممدوح صبحى: 01220068681"
+        },
+        {
+            "question": "1- مزمور الرَّبُّ قَدْ مَلكَ",
+            "wight": "5",
+            "answer": "اَلرَّبُّ قَدْ مَلَكَ. لَبِسَ الْجَلاَلَ. لَبِسَ الرَّبُّ الْقُدْرَةَ، ائْتَزَرَ بِهَا. أَيْضًا تَثَبَّتَتِ الْمَسْكُونَةُ. لاَ تَتَزَعْزَعُ. كُرْسِيُّكَ مُثْبَتَةٌ مُنْذُ الْقِدَمِ. مُنْذُ الأَزَلِ أَنْتَ. رَفَعَتِ الأَنْهَارُ يَا رَبُّ، رَفَعَتِ الأَنْهَارُ صَوْتَهَا. تَرْفَعُ الأَنْهَارُ عَجِيجَهَا. مِنْ أَصْوَاتِ مِيَاهٍ كَثِيرَةٍ، مِنْ غِمَارِ أَمْوَاجِ الْبَحْرِ، الرَّبُّ فِي الْعُلَى أَقْدَرُ. شَهَادَاتُكَ ثَابِتَةٌ جِدًّا. بِبَيْتِكَ تَلِيقُ الْقَدَاسَةُ يَا رَبُّ إِلَى طُولِ الأَيَّامِ."
+        },
+        {
+            "question": "2- مزمور اللَّهُمَّ إلْتَفتْ إلى معونتي",
+            "wight": "5",
+            "answer": "اللهم التفت إلى معونتي، يا رب أسرع وأعنى. ليَخزَ ويخجل طالبو نفسي، وليرتد إلى خلف ويخجل الذين يبتغون لي الشر. وليرجع بالخزي سريعا القائلون لي: نِعِمَّا نِعِمَّا. وليبتهج ويفرح بك جميع الذين يلتمسونك، وليقل في كل حين محبو خلاصك: فليتعظم الرب. وأما أنا فمسكين وفقير، اللهم أعنى. أنت معيني ومخلصي يا رب فلا تبطئ.هلليلويا."
+        },
+        {
+            "question": "3- إنجيل الساعة السادسة",
+            "wight": "10",
+            "answer": "فلما أبصر الجموع صعد إلى الجبل. وعندما جلس تقدم إليه تلاميذه، ففتح فاه وعلمهم قائلا: طوبى للمساكين بالروح، لأن لهم ملكوت السموات. طوبى للحزانى الآن، لأنهم يتعزون. طوبى للودعاء، لأنهم يرثون الأرضَ. طوبى للجياع والعطاش إلى البر لأنهم يُشبعون. طوبى للرحماء لأنهم يُرحمون. طوبى لأنقياء القلب لأنهم يعاينون الله. طوبى لصانعي السلام، لأنهم يُدعَون أبناءَ الله. طوبى للمطرودين من أجل البر لأن لهم ملكوت السموات. طوبى لكم إذا طردوكم وعيروكم وقالوا فيكم من أجلي كل شر كاذبين. افرحوا وتهللوا لأن أجركم عظيم في السموات، فإنهم هكذا طردوا الأنبياء الذين كانوا قبلكم.            أنتم مِلح الأرض، فإذا فسد المِلح فبماذا يُملح؟ لا يصلح بعد لشيء، إلا لأن يطرح خارجا وتدوسه الناس. أنتم نور العالم. لا يمكن أن تخفى مدينة كائنة على جبل. ولا يوقدون سراجا ويضعونه تحت المكيال، بل يضعونه على المنارة فيضيء لكل من في البيت. هكذا فليضئ نوركم قدام الناس، لكي يروا أعمالكم الصالحة فيمجدوا أباكم الذي في السموات. (والمجد لله دائما)"
+        }
+    ]</t>
+  </si>
+  <si>
+    <t>[
+        {
+            "instructions": "في حالة وجود أي استفسار يُرجَي الرجوع لخدام المادة:  أ/ سمير فهمى: 01220068681"
+        },
+        {
+            "question": "1- مزمور سبحوا الرب تسبيحاً جديداً",
+            "wight": "5",
+            "answer": "سبحوا الرب تسبيحا جديدا لأن الرب قد صنع أعمالا عجيبة، خلصتْ له يمينه وذراعه القدوس، أعلن الرب خلاصه وكشف قدام الأمم عدله. ذكر رحمته ليعقوب وحقه لبيت إسرائيل. نظرت أقاصي الأرض جميعا خلاص إلهنا.            هللوا للرب يا كل الأرض، سبحوا وهللوا ورتلوا. رتلوا للرب بالقيثارة، بالقيثارة وصوت المزمار. بأبواق خافقة وصوت بوق القرن، هللوا أمام الرب الملك. فليعج البحر وكل ملئه، المسكونة وكل الساكنين فيها. تصفق جميع الأنهار، الجبال تبتهج أمام وجه الرب، لأنه أتى ليدين الأرض، يدين المسكونة بالعدل والشعوب بالاستقامة هلليلويا."
+        },
+        {
+            "question": "2- مزمور سبحوا الرب أيها الفتيان",
+            "wight": "5",
+            "answer": "سبحوا الرب أيها الفتيان، سبحوا اسم الرب. ليكن اسم الرب مباركا من الآن وإلى الأبد. من مشارق الشمس إلى مغاربها باركوا اسم الرب. الرب عالٍ على كل الأمم، فوق السموات مجده. من مثل الرب إلهنا؟!‍ الساكن في الأعالي، الناظِر إلى المتواضعين في السماء وعلى الأرض. المقيم المسكين من التراب، الرافع البائس من المِزْبَلة لكي يُجلسه مع رؤساء شعبه. الذي يجعل العاقرَ ساكنة في بيت، أم أولادٍ فرحة. هلليلويا."
+        },
+        {
+            "question": "3- إنجيل الساعة التاسعة",
+            "wight": "10",
+            "answer": "ولما رجع الرسل حدثوه بما فعلوا. فأخذهم معه ودخل على انفرادٍ مدينة تسمى بيتَ صيدا. فلما علمت الجموع تبعوه فقبلهم وخاطبهم عن ملكوت الله، والمحتاجون إلى الشفاء شفاهم. وكان النهار قد بدأ يميل فتقدم إليه الاثنا عشر وقالوا له: اصرف الجموع ليذهبوا إلى القرى المحيطة والحقول، ليستريحوا ويجدوا ما يأكلونه، فإننا ههنا في موضع قفر. فقال لهم: أعطوهم أنتم ليأكلوا. فقالوا: ليس عندنا أكثر من خمس خبزات وسمكتين، إلا أن نمضي نحن ونشتري أطعمة لهذا الشعب جميعه. وكانوا نحو خمسة آلاف رجل. فقال لتلاميذه: ليتكئوا في كل موضع خمسين خمسين. ففعلوا هكذا وأتكأوهم أجمعين. فأخذ الخمسَ خبزاتٍ والسمكتين، ونظر إلى السماء، وباركها وقسمها، وأعطى التلاميذ ليضعوا أمام الجموع. فأكلوا جميعهم وشبعوا. ثم رفعوا ما فضل عنهم اثنتي عشرة قفة مملوءة. (والمجد لله دائما)"
+        }
+    ]</t>
+  </si>
+  <si>
+    <t>[
+        {
+            "instructions": "في حالة وجود أي استفسار يُرجَي الرجوع لخدام المادة:  أ/ عصام عاجيبى: 01220068681"
+        },
+        {
+            "question": "1. سبحوا الربَّ يا جميع الأمم",
+            "wight": "2",
+            "answer": "سبحوا الربَّ يا جميع الأمم ولتباركه كافة الشعوب. لأن رحمته قد ثبتت علينا وحق الرب يدوم إلى الأبد هلليلويا."
+        },
+        {
+            "question": "2. رفعت عيني إلي الجبال",
+            "wight": "4",
+            "answer": "رفعت عيني إلى الجبال، من حيث يأتي عوني. معونتي من عند الرب الذي صنع السماء والأرض. لا يسلم رجلك للزلل، فما ينعس حافظك. هوذا لا ينعس ولا ينام حارس إسرائيل. الرب يحفظك. الرب يظلل على يدك اليمنى، فلا تحرقك الشمس بالنهار ولا القمر بالليل. الرب يحفظك من كل سوء. الرب يحفظ نفسك. الرب يحفظ دخولك وخروجك، من الآن والي الأبد هلليلويا."
+        },
+        {
+            "question": "3. فرحت بالقائلين لي إلي بيت الرب نذهب",
+            "wight": "4",
+            "answer": "فرحت بالقائلين لي إلى بيت الرب نذهب. وقفت أرجلنا في ديار أورشليم، أورشليم المبنية مثل مدينة متصلة بعضها ببعض. لأن هناك صعدت القبائل، قبائل الرب، شهادة لإسرائيل، يعترفون لاسم الرب. هناك نصبت كراسي للقضاء كراسي بيت داود.اسألوا السلام لأورشليم والخصبَ لمحبيك. ليكن السلام في حصنك والخصب في أبراجك الرصينة. من أجل اخوتي وأقربائي تكلمت من أجلك بالسلام، ومن أجل بيت الرب إلهنا التمست لك الخيرات هلليلويا."
+        },
+        {
+            "question": "4. إنجيل صلاة الغروب",
+            "wight": "10",
+            "answer": "ولما قام من المجمع دخل بيت سمعان. وكانت حماة سمعان بحمَّى شديدة. فسألوه من أجلها. فوقف فوقا منها وانتهر الحمى، فتركتها وفي الحال قامت وخدمتهم. وعند غروب الشمس كان كل الذين عندهم مرضى بأنواع أمراض كثيرة يقدمونهم إليه. أما هو فكان يضع يديه على كل واحد منهم فيشفيهم. وكانت الشياطين تخرج من كثيرين وهي تصرخ وتقول: أنت هو المسيح ابن الله. فكان ينتهرهم ولا يدَعهم ينطقون، لأنهم كانوا قد عرفوه أنه هو المسيح (والمجد لله دائما)"
+        }
+    ]</t>
+  </si>
+  <si>
+    <t>[
+        {
+            "instructions": "في حالة وجود أي استفسار يُرجَي الرجوع لخدام المادة:  أ/ هانى فريد: 01220068681"
+        },
+        {
+            "question": "1- مزمور من الأعماق صرخت إليك يارب",
+            "wight": "5",
+            "answer": "من الأعماق صرخت إليك يا رب. يا رب استمع صوتي، لتكن أذناك مصغيتين إلى صوت تضرعي. إن كنت للآثام راصدا يا رب، يا رب من يثبت لأن من عندك المغفرة. من أجل اسمك صبرْتُ لك يا رب، صبرَتْ نفسي لناموسك. انتظرت نفسي الرب من محرس الصبح إلى الليل. من محرس الصبح فلينتظر إسرائيل الرب. لأن الرحمة من عند الرب. عظيم هو خلاصه وهو يفتدي إسرائيل من كل آثامه. هلليلويا"
+        },
+        {
+            "question": "2- مزمور ها باركو الرب",
+            "wight": "5",
+            "answer": "ها باركوا الربَّ يا عبيدَ الرب، القائمين في بيت الرب في ديار إلهنا. في الليالي ارفعوا أيديكم إلى القدس وباركوا الرب. يبارككم الرب من صهيون الذي خلق السماء والأرض. هلليلويا."
+        },
+        {
+            "question": "3- مزمور سبحي يا نفسي الرب",
+            "wight": "5",
+            "answer": "سبحي يا نفسي الربَّ. أسبح الرب في حياتي، وأرتل لإلهي ما دمت موجودا. لا تتكلوا على الرؤساء ولا على بني البشر الذين ليس عندهم خلاص. تخرج روحهم فيعودون إلى ترابهم. في ذلك اليوم تهلك كافة أفكارهم. طوبى لمن إله يعقوب معينه. واتكاله على الرب إلهه، الذي صنع السماء والأرض والبحر وكل ما فيها. الحافظ العدل إلى الدهر، الصانع الحكم للمظلومين المعطي الطعام للجياع. الرب يحل المربوطين الرب يقيم الساقطين. الرب يُحَكِّم العميان. الرب يحب الصديقين. الرب يحفظ الغرباء، ويعضد اليتيم والأرملة. ويبيد طرق الخطاة. يملك الرب إلى الدهر، وإلهك يا صهيون من جيل إلى جيل. هلليلويا."
+        },
+        {
+            "question": "4- إنجيل صلاة النوم",
+            "wight": "5",
+            "answer": "وإذا انسان كان بأورشليم اسمه سمعان وهذا الإنسان كان بار اً تقيا، متوقعا تعزية إسرائيل، والروح القدس كان عليه. وكان قد أعلم بوحي من الروح القدس أنه لا يرى الموت قبل أن يعاين المسيح الرب. فأقبل بالروح إلى الهيكل. ولما دخل بالطفل يسوع أبواه ليصنعا عنه كما يجب في الناموس. حمله سمعان على ذراعيه وبارك الله قائلا : الآن يا سيد تطلق عبدك بسلام حسب قولك. لأن عيني قد أبصرتا خلاصك. الذي أعددته قدام جميع الشعوب. نورا تجلي للأمم، ومجد اً لشعبك اسرائيل.والمجد لله دائماً."
+        }
+    ]</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> [
+        {
+            "instructions": "علي الخادم نُطْقْ الكلمة للمخدوم لأن المخدوم حافظ الكلمة سماعي فقط لا يستطيع القراءة+في حالة وجود أي استفسار يُرجَي الرجوع لخدام المادة:+ت/ ماريا إيليا (01203735337)+ت/ مريم جرجس ( 01286621080 )"
+        },
+        {
+            "question": "1- Ⲁ ⲁ",
+            "wight": "3"
+        },
+        {
+            "question": "2- Ⲇ ⲇ",
+            "wight": "3"
+        },
+        {
+            "question": "3- ⲋ ⲋ",
+            "wight": "3"
+        },
+        {
+            "question": "4- Ⲍ ⲍ",
+            "wight": "3"
+        },
+        {
+            "question": "5- Ⲏ ⲏ",
+            "wight": "3"
+        },
+        {
+            "question": "6- Ⲑ ⲑ",
+            "wight": "3"
+        },
+        {
+            "question": "7- Ⲉ ⲉ",
+            "wight": "3"
+        },
+        {
+            "question": "8- Ⳉ ⳉ",
+            "wight": "3"
+        },
+        {
+            "question": "9- Ⲓ ⲓ",
+            "wight": "3"
+        },
+        {
+            "question": "10- Ⲃ ⲃ",
+            "wight": "3"
+        },
+        {
+            "question": "11- ̀Ⲉⲃⲓⲱ عسل",
+            "wight": "5"
+        },
+        {
+            "question": "12- Ⲁⲫⲉ  رأس",
+            "wight": "5"
+        },
+        {
+            "question": "13- Ⲁⲛⳉⳉⲉⲗⲟⲥ  ملاك",
+            "wight": "5"
+        },
+        {
+            "question": "14- Ⲍⲉⲛⲍⲉⲛ  سحلية",
+            "wight": "5"
+        },
+        {
+            "question": "15- Ⲓⲁⲗ مراية",
+            "wight": "5"
+        }
+    ]</t>
+  </si>
+  <si>
+    <t>[
+        {
+            "instructions": "علي الخادم نُطْقْ الكلمة للمخدوم لأن المخدوم حافظ الكلمة سماعي فقط لا يستطيع القراءة+في حالة وجود أي استفسار يُرجَي الرجوع لخدام المادة:+ت/ مارينا صموئيل ( 01208866481 )+ت/ كاترين فتح الله ( 01273502395 )+ت/ مارينا فتح الله (01287124457))"
+        },
+        {
+            "question": "1-  ( Ϣⲁϣϥ - `Ϣⲙⲏⲛ - Ϣⲁϥⲉ ) رقم 7  تعني",
+            "wight": "2"
+        },
+        {
+            "question": "2-  ( كرسى - غرفة - حائط )  Ϭⲗⲟ تعنى",
+            "wight": "2"
+        },
+        {
+            "question": "3-  ( Ⲥⲟⲩⲣⲓ - Ⲱⲛⲓ - Ⲧⲟⲧⲥ ) شوكة تعني",
+            "wight": "2"
+        },
+        {
+            "question": "4-  ( شباك - شارع - نحلة ) Ⲕⲁⲑⲏⲟⲩ تعني",
+            "wight": "2"
+        },
+        {
+            "question": "5-  ( Ⲕⲁϫⲓ - Ⲯⲩⲭⲟⲥ - Ⲟⲩⲁⲓ ) رقم 1  تعني",
+            "wight": "2"
+        },
+        {
+            "question": "6-  اذكر رقم 7",
+            "wight": "2"
+        },
+        {
+            "question": "7-  اذكر رقم 3",
+            "wight": "2"
+        },
+        {
+            "question": "8-  اذكر رقم 8",
+            "wight": "2"
+        },
+        {
+            "question": "9-  اذكر رقم 9",
+            "wight": "2"
+        },
+        {
+            "question": "10-  اذكر رقم 10",
+            "wight": "2"
+        },
+        {
+            "question": "11- Ⲛ - Ⲏ -  Ⲧ - Ⲟ - Ⲩ - Ⲇ اذكر قاعدة الحروف الآتية : (اختر حرف و لا يكرر فى السوال التالى)",
+            "wight": "4"
+        },
+        {
+            "question": "12- Ⲛ - Ⲏ -  Ⲧ - Ⲟ - Ⲩ - Ⲇ  اذكر قاعدة الحروف الآتية : (اختر حرف و لا يكرر فى السوال التالى)",
+            "wight": "4"
+        },
+        {
+            "question": "13- Ⲛ - Ⲏ -  Ⲧ - Ⲟ - Ⲩ - Ⲇ  اذكر قاعدة الحروف الآتية : (اختر حرف و لا يكرر فى السوال التالى)",
+            "wight": "4"
+        },
+        {
+            "question": "14- Ⲛ - Ⲏ -  Ⲧ - Ⲟ - Ⲩ - Ⲇ  اذكر قاعدة الحروف الآتية : (اختر حرف و لا يكرر فى السوال التالى)",
+            "wight": "4"
+        },
+        {
+            "question": "15- Ⲛ - Ⲏ -  Ⲧ - Ⲟ - Ⲩ - Ⲇ  اذكر قاعدة الحروف الآتية : (اختر حرف و لا يكرر فى السوال التالى)",
+            "wight": "4"
+        },
+        {
+            "question": "16- ",
+            "wight": "3"
+        },
+        {
+            "question": "17-",
+            "wight": "3"
+        },
+        {
+            "question": "18-  رقم 6 ينطف Ϣⲟⲙⲧ",
+            "wight": "3"
+        },
+        {
+            "question": "19-  دانيال يعنى Ⲇⲁⲛⲓⲏⲗ",
+            "wight": "3"
+        },
+        {
+            "question": "20-  سماء يعنى Ⲫⲉ",
+            "wight": "3"
+        },
+        {
+            "question": "21-  حروف اللغة القبطى منقسمين الى 3 اقسام اذكرهم ",
+            "wight": "5"
+        },
+        {
+            "question": "22-  معني حواء",
+            "wight": "5"
+        },
+        {
+            "question": "23-  معني كرسي ",
+            "wight": "5"
+        },
+        {
+            "question": "24-  معنى غرفة",
+            "wight": "5"
+        },
+        {
+            "question": "25-  كم عدد الحروف المتحركة القابلة للكسر؟ وما هم ؟ ",
+            "wight": "5"
+        },
+        {
+            "question": "26-  ما هي اسم العلامة التي توضع فوق الحروف وتنطق ( إ ) أو همزة ؟  ",
+            "wight": "5"
+        },
+        {
+            "question": "27-",
+            "wight": "5"
+        }
+    ]</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> [
+        {
+            "instructions": "في حالة وجود أي استفسار يُرجَي الرجوع لخدام المادة:+أ/ مينا ابراهيم  أ/ بيشوى جوزيف     "
+        },
+        {
+            "question": "1-\tإيه بى إبروس إيـﭭشى إسطاثى تيه",
+            "wight": "5"
+        },
+        {
+            "question": "2- إبروس إيڤ إكصاستيه ",
+            "wight": "5"
+        },
+        {
+            "question": "3- بشفاعات والدة الإله ",
+            "wight": "10"
+        },
+        {
+            "question": "4- الشاروبيم يسجدون لك ",
+            "wight": "10"
+        },
+        {
+            "question": "5-\tأيها الجلوس قفوا (عربى) ",
+            "wight": "5"
+        },
+        {
+            "question": "6-\tوإلى الشرق أنظروا (عربى) ",
+            "wight": "5"
+        },
+        {
+            "question": "7-\tننصت (قبطي وعربي) \n(قبطى- 2.5 درجة)  و (عربى-2.5 درجة)",
+            "wight": "5"
+        },
+        {
+            "question": "8-\tأسجدوا لله بخوف ورعدة (عربى) ",
+            "wight": "5"
+        },
+        {
+            "question": "9-\tننصت آمين (قبطى وعربى)\n (قبطى- 5 درجات)  و (عربى-5 درجات)",
+            "wight": "10"
+        },
+        {
+            "question": "10-\tآمين آمين صلوا (قبطى وعربى)\n (قبطى- 5 درجات)  و (عربى-5 درجات)  ",
+            "wight": "10"
+        }
+    ]</t>
+  </si>
+  <si>
+    <t>[
+        {
+            "instructions": "في حالة وجود أي استفسار يُرجَي الرجوع لخدام المادة:+أ/ مينا ابراهيم  أ/ بيشوى جوزيف     "
+        },
+        {
+            "question": "1-\tآمين آمين آمين بموتك يارب نبشر (عربى)",
+            "wight": "20"
+        },
+        {
+            "question": "2- حل وإغفر (حتي كلمة الخفية والظاهرة)",
+            "wight": "20"
+        },
+        {
+            "question": "3- صلوا من أجل الإنجيل المقدس (قبطى وعربى)\n (قبطى- 5 درجات)  و (عربى-5 درجات) ",
+            "wight": "10"
+        },
+        {
+            "question": "4- إسطاثى تيه ميه طا فوﭭو ثيه أو ",
+            "wight": "10"
+        },
+        {
+            "question": "5-\tطوبى للرحماء على المساكین ",
+            "wight": "10"
+        },
+        {
+            "question": "6-\tمردات أناجیل أحد الشعانین\n(4مردات * 10 درجات) ",
+            "wight": "40"
+        }
+    ]</t>
+  </si>
+  <si>
+    <t>[
+        {
+            "instructions": "في حالة وجود أي استفسار يُرجَي الرجوع لخدام المادة:+أ/ مينا ابراهيم  أ/ بيشوى جوزيف     "
+        },
+        {
+            "question": "1-\tالليلويا فاى بيه بى",
+            "wight": "20"
+        },
+        {
+            "question": "2- تى شورى",
+            "wight": "20"
+        },
+        {
+            "question": "3- هيتينية السيدة العذراء مريم ",
+            "wight": "5"
+        },
+        {
+            "question": "4-   هيتينية الملائكة ",
+            "wight": "5"
+        },
+        {
+            "question": "4-   هيتينية ماريوحنا المعمدان ",
+            "wight": "5"
+        }
+    ]</t>
+  </si>
+  <si>
+    <t>[
+        {
+            "instructions": "في حالة وجود أي استفسار يُرجَي الرجوع لخدام المادة:+أ/ كلوج رسمى  أ/ ميلاد يلسر    "
+        },
+        {
+            "question": "1-\tإسباتير آجيوس",
+            "wight": "15"
+        },
+        {
+            "question": "2- الليلويا فاى بيه بى",
+            "wight": "15"
+        },
+        {
+            "question": "3- الليلويا ﭽيه إف ميـﭭـى ",
+            "wight": "15"
+        },
+        {
+            "question": "4- تى شورى ",
+            "wight": "20"
+        },
+        {
+            "question": "5-\tهيتينية السيدة العذراء مريم، هيتينية الملائكة\n(2 * 5= 10) ",
+            "wight": "10"
+        },
+        {
+            "question": "6-\t هيتينية ماريوحنا المعمدان، هيتينية الرسل\n(2 * 5= 10)",
+            "wight": "10"
+        },
+        {
+            "question": "7-\t هيتين نى إبريسـﭭيا (الختام الباسيلى السريع)",
+            "wight": "15"
+        }
+    ]</t>
+  </si>
+  <si>
+    <t>[
+        {
+            "instructions": "في حالة وجود أي استفسار يُرجَي الرجوع لخدام المادة:+أ/ كلوج رسمى  أ/ ميلاد يلسر    "
+        },
+        {
+            "question": "1-\tالليلويا ﭽيه إف ميـﭭـى",
+            "wight": "15"
+        },
+        {
+            "question": "2- هيتينية الرسل، هيتينية مارمرقس\n(2*5 درجات)",
+            "wight": "10"
+        },
+        {
+            "question": "3- هيتينية القديس إسطفانوس، هيتينية مارجرجس\n(2*5 درجات) ",
+            "wight": "10"
+        },
+        {
+            "question": "4-   هيتينية أبو سيفين، هيتينية مارمينا\n(2*5 درجات) ",
+            "wight": "10"
+        },
+        {
+            "question": "5-   هيتينية القديسة دميانة، هيتينية الأنبا بيشوى\n(2*5 درجات) ",
+            "wight": "10"
+        },
+        {
+            "question": "6-   هيتينية الأنبا كاراس، هيتينية ق. كسيموس ودوماديوس\n(2*5 درجات) ",
+            "wight": "10"
+        },
+        {
+            "question": "7-  هيتين ني إبريسـﭭيا (الختام الباسيلي السريع) ",
+            "wight": "15"
+        }
+    ]</t>
+  </si>
+  <si>
+    <t>[
+        {
+            "instructions": "في حالة وجود أي استفسار يُرجَي الرجوع لخدام المادة:+أ/ ابانوب جوزيف  أ/ جورج ابراهيم    "
+        },
+        {
+            "question": "1-\tالليلويا ﭽيه إف ميـﭭـى",
+            "wight": "15"
+        },
+        {
+            "question": "2- هيتينية الرسل، هيتينية مارمرقس\n(2*5 درجات)",
+            "wight": "10"
+        },
+        {
+            "question": "3- هيتينية القديس إسطفانوس، هيتينية مارجرجس\n(2*5 درجات) ",
+            "wight": "10"
+        },
+        {
+            "question": "4-   هيتينية أبو سيفين، هيتينية مارمينا\n(2*5 درجات) ",
+            "wight": "10"
+        },
+        {
+            "question": "5-   هيتينية القديسة دميانة، هيتينية الأنبا بيشوى\n(2*5 درجات) ",
+            "wight": "10"
+        },
+        {
+            "question": "6-   هيتينية الأنبا كاراس، هيتينية ق. كسيموس ودوماديوس\n(2*5 درجات) ",
+            "wight": "10"
+        },
+        {
+            "question": "7-   هيتينية قديسى اليوم، هيتينية البابا\n(2*5 درجات) ",
+            "wight": "10"
+        },
+        {
+            "question": "8-  هيتينية الأسقف ",
+            "wight": "5"
+        }
+    ]</t>
+  </si>
+  <si>
+    <t>[
+        {
+            "instructions": "في حالة وجود أي استفسار يُرجَي الرجوع لخدام المادة:+أ/ ابانوب جوزيف  أ/ جورج ابراهيم    "
+        },
+        {
+            "question": "1-\tأوشية السلام (عربى)",
+            "wight": "5"
+        },
+        {
+            "question": "2- أوشية الآباء (عربى)- عشية وباكر وقداس.",
+            "wight": "10"
+        },
+        {
+            "question": "3- أوشية المرضى (عربى) ",
+            "wight": "10"
+        },
+        {
+            "question": "4-  أوشية المسافرين (عربى) ",
+            "wight": "10"
+        },
+        {
+            "question": "5-\tأوشية الموضع (قبطى وعربى) - عشية وباكر وقداس\n(5 درجات عربي) و (10 درجات قبطي) ",
+            "wight": "15"
+        },
+        {
+            "question": "6-\t أوشية الاجتماعات (قبطى، عربى)\n(5 درجات عربي) و (10 درجات قبطي)",
+            "wight": "15"
+        },
+        {
+            "question": "7-\t تين جوشت إيـﭭول خا إتهى (عشية وباكر وقداس)\n(10 درجات عشية وباكر) و (10 درجات قداس)",
+            "wight": "20"
+        },
+        {
+            "question": "8-\t مرد إنجيل باكر السنوي (مارين أو أوأوشت)",
+            "wight": "10"
+        }
+    ]</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> [
+        {
+            "instructions": "في حالة وجود أي استفسار يُرجَي الرجوع لخدام المادة:+أ/ ابانوب جوزيف  أ/ جورج ابراهيم    "
+        },
+        {
+            "question": "1-\tأوشية السلام (عربى)",
+            "wight": "5"
+        },
+        {
+            "question": "2- أوشية الآباء (عربى)- عشية وباكر وقداس.",
+            "wight": "10"
+        },
+        {
+            "question": "3- أوشية المرضى (عربى) ",
+            "wight": "10"
+        },
+        {
+            "question": "4-  أوشية المسافرين (عربى) ",
+            "wight": "10"
+        },
+        {
+            "question": "5-\tأوشية الموضع (قبطى وعربى) - عشية وباكر وقداس\n(5 درجات عربي) و (10 درجات قبطي) ",
+            "wight": "15"
+        },
+        {
+            "question": "6-\t أوشية الاجتماعات (قبطى، عربى)\n(5 درجات عربي) و (10 درجات قبطي)",
+            "wight": "15"
+        },
+        {
+            "question": "7-\t تين جوشت إيـﭭول خا إتهى (عشية وباكر وقداس)\n(10 درجات عشية وباكر) و (10 درجات قداس)",
+            "wight": "20"
+        },
+        {
+            "question": "8-\t مرد إنجيل باكر السنوي (مارين أو أوأوشت)",
+            "wight": "10"
+        },
+        {
+            "question": "9-\t ﭭـول إيـﭭول",
+            "wight": "20"
+        }
+    ]</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> [
+        {
+            "instructions": "في حالة وجود أي استفسار يُرجَي الرجوع لخدام المادة:+أ/ كيرلس حبشى    "
+        },
+        {
+            "question": "1- أوس بيه رين",
+            "wight": "10"
+        },
+        {
+            "question": "2- إس أو بان آجيوس باتير",
+            "wight": "10"
+        },
+        {
+            "question": "3- مرد الإبركسيس السنوى",
+            "wight": "20"
+        },
+        {
+            "question": "4- ﭭـول إيـﭭول",
+            "wight": "20"
+        },
+        {
+            "question": "5- مزمور التوزيع السنوى (عربى) (تسميع 3 أرباع فقط * 5 درجات كل ربع)",
+            "wight": "15"
+        },
+        {
+            "question": "6-  مزمور التوزيع السنوى (قبطي) (تسميع 3 أرباع فقط * 5 درجات كل ربع)",
+            "wight": "15"
+        }
+    ]</t>
+  </si>
+  <si>
+    <t>[
+        {
+            "instructions": "في حالة وجود أي استفسار يُرجَي الرجوع لخدام المادة:+أ/ كيرلس حبشى    "
+        },
+        {
+            "question": "1-\t أوشية الراقدين (عريى)",
+            "wight": "15"
+        },
+        {
+            "question": "2- أوشية القارابين (قبطى)",
+            "wight": "10"
+        },
+        {
+            "question": "3- أوشية القسوس (عربى)",
+            "wight": "10"
+        },
+        {
+            "question": "4- قبلوا بعضكم الصغيرة (عربى)",
+            "wight": "15"
+        },
+        {
+            "question": "5- أوس بيه رين",
+            "wight": "10"
+        },
+        {
+            "question": "6- إس أو بان آجيوس باتير",
+            "wight": "10"
+        },
+        {
+            "question": "7- مرد الإبركسيس السنوى",
+            "wight": "20"
+        },
+        {
+            "question": "8- مزمور التوزيع السنوى (قبطي) (تسميع 3 أرباع فقط * 5 درجات كل ربع)",
+            "wight": "15"
+        }
+    ]</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> [
+        {
+            "instructions": "في حالة وجود أي استفسار يُرجَي الرجوع لخدام المادة:+أ/ كيرلس حبشى    "
+        },
+        {
+            "question": "1-\t أوشية الراقدين (عريى)",
+            "wight": "15"
+        },
+        {
+            "question": "2- أوشية القارابين (عريى)",
+            "wight": "10"
+        },
+        {
+            "question": "3- أوشية القسوس (عربى)",
+            "wight": "10"
+        },
+        {
+            "question": "4- قبلوا بعضكم الصغيرة (عربى)",
+            "wight": "15"
+        },
+        {
+            "question": "5- أوس بيه رين",
+            "wight": "10"
+        },
+        {
+            "question": "6- إس أو بان آجيوس باتير",
+            "wight": "10"
+        },
+        {
+            "question": "7- مرد الإبركسيس السنوى",
+            "wight": "20"
+        },
+        {
+            "question": "8- مزمور التوزيع السنوى (قبطي) (تسميع 3 أرباع فقط * 5 درجات كل ربع)",
+            "wight": "15"
+        }
+    ]</t>
+  </si>
+  <si>
+    <t>[
+        {
+            "instructions": "في حالة وجود أي استفسار يُرجَي الرجوع لخدام المادة:+أ/ اشرف موريس    "
+        },
+        {
+            "question": "1-\t أوشية الراقدين (عريى)",
+            "wight": "15"
+        },
+        {
+            "question": "2- أوشية القارابين (قبطى)",
+            "wight": "10"
+        },
+        {
+            "question": "3- أوشية القسوس (عربى)",
+            "wight": "10"
+        },
+        {
+            "question": "4- قبلوا بعضكم الصغيرة (عربى)",
+            "wight": "15"
+        },
+        {
+            "question": "5- أوس بيه رين",
+            "wight": "10"
+        },
+        {
+            "question": "6- إس أو بان آجيوس باتير",
+            "wight": "10"
+        },
+        {
+            "question": "7- مرد الإبركسيس السنوى",
+            "wight": "20"
+        },
+        {
+            "question": "8- مزمور التوزيع السنوى (قبطي) (تسميع 3 أرباع فقط * 5 درجات كل ربع)",
+            "wight": "15"
+        }
+    ]</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> [
+        {
+            "instructions": "في حالة وجود أي استفسار يُرجَي الرجوع لخدام المادة:+أ/ اشرف موريس    "
+        },
+        {
+            "question": "1- أوشية السلام (قبطى )",
+            "wight": "10"
+        },
+        {
+            "question": "2- أوشية الآباء (قبطى) - عشية وباكر وقداس",
+            "wight": "15"
+        },
+        {
+            "question": "3- أوشية المرضى (قبطى)",
+            "wight": "15"
+        },
+        {
+            "question": "4-  أوشية المسافرين (قبطى)",
+            "wight": "15"
+        },
+        {
+            "question": "5- أرباع الناقوص الواطس (2*5 درجات)",
+            "wight": "10"
+        },
+        {
+            "question": "6- أرباع الناقوص الآدام (4*5 درجات)",
+            "wight": "20"
+        },
+        {
+            "question": "7- أرباع الناقوص للعذراء، الملاك ميخائيل، الملاك غبريال  (3*5 درجات)",
+            "wight": "15"
+        },
+        {
+            "question": "8- أرباع الناقوص للملاك ميخائيل وغبريال،    الشاروبيم والسيرافيم.، الرسل  (3*5 درجات)",
+            "wight": "15"
+        },
+        {
+            "question": "9-أرباع الناقوص لمارمرقس، الشهيد إسطفانوس، مارجرجس   (3*5 درجات)",
+            "wight": "15"
+        },
+        {
+            "question": "10-أرباع الناقوص لأبي سيفين، مارمينا، القديسة دميانة   (3*5 درجات)",
+            "wight": "15"
+        }
+    ]</t>
+  </si>
+  <si>
+    <t>[
+        {
+            "instructions": "في حالة وجود أي استفسار يُرجَي الرجوع لخدام المادة:+أ/ اشرف موريس    "
+        },
+        {
+            "question": "1- ذوكصولوجية مارجرجس   تسميع 3 أرباع فقط  (3 *5 درجات )",
+            "wight": "15"
+        },
+        {
+            "question": "2- ذوكصولوجية مارمينا  تسميع 3 أرباع فقط  (3 *5 درجات )",
+            "wight": "15"
+        },
+        {
+            "question": "3- لحن البركة (تين أوأوشت) بالبرلكس",
+            "wight": "20"
+        }
+    ]</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> [
+        {
+            "instructions": "في حالة وجود أي استفسار يُرجَي الرجوع لخدام المادة:+أ/ رامى رافت    "
+        },
+        {
+            "question": "1- ذوكصولوجية الرسل        تسميع 3 أرباع فقط  (3 *5 درجات )",
+            "wight": "15"
+        },
+        {
+            "question": "2- ذوكصولوجية مارمرقص   تسميع 3 أرباع فقط  (3 *5 درجات )",
+            "wight": "15"
+        },
+        {
+            "question": "3- ذوكصولوجية الشهيد إسطفانوس  تسميع 3 أرباع فقط  (3 *5 درجات )",
+            "wight": "15"
+        },
+        {
+            "question": "4-  ذوكصولوجية مارجرجس  تسميع 3 أرباع فقط  (3 *5 درجات )",
+            "wight": "15"
+        },
+        {
+            "question": "5-  ذوكصولوجية أبى سيفين  تسميع 3 أرباع فقط  (3 *5 درجات )",
+            "wight": "15"
+        },
+        {
+            "question": "6-  ذوكصولوجية مارمينا تسميع 3 أرباع فقط  (3 *5 درجات )",
+            "wight": "15"
+        }
+    ]</t>
+  </si>
+  <si>
+    <t>[
+        {
+            "instructions": "في حالة وجود أي استفسار يُرجَي الرجوع لخدام المادة:+أ/ رامى رافت    "
+        },
+        {
+            "question": "1- ذوكصولوجية الرسل        تسميع 3 أرباع فقط  (3 *5 درجات )",
+            "wight": "15"
+        },
+        {
+            "question": "2- ذوكصولوجية مارمرقص   تسميع 3 أرباع فقط  (3 *5 درجات )",
+            "wight": "15"
+        },
+        {
+            "question": "3- ذوكصولوجية الشهيد إسطفانوس  تسميع 3 أرباع فقط  (3 *5 درجات )",
+            "wight": "15"
+        },
+        {
+            "question": "4-  ذوكصولوجية مارجرجس  تسميع 3 أرباع فقط  (3 *5 درجات )",
+            "wight": "15"
+        },
+        {
+            "question": "5-  ذوكصولوجية أبى سيفين  تسميع 3 أرباع فقط  (3 *5 درجات )",
+            "wight": "15"
+        },
+        {
+            "question": "6-  ذوكصولوجية مارمينا تسميع 3 أرباع فقط  (3 *5 درجات )",
+            "wight": "15"
+        },
+        {
+            "question": "7-  ذوكصولوجية القديسة دميانة تسميع 3 أرباع فقط  (3 *5 درجات )",
+            "wight": "15"
+        }
+    ]</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> [
+        {
+            "instructions": "في حالة وجود أي استفسار يُرجَي الرجوع لخدام المادة:+أ/ رامى رافت    "
+        },
+        {
+            "question": "1- لحن إبؤرو الطويل  تسميع ربعين فقط  (2 *15 درجة )",
+            "wight": "30"
+        },
+        {
+            "question": "2- بى نيشتى",
+            "wight": "20"
+        },
+        {
+            "question": "3- أرباع ناقوص شهر كيهك  (ربعين * 5 درجات)",
+            "wight": "10"
+        },
+        {
+            "question": "4- هيتينيات شهر كيهك   (4 * 5 درجات)",
+            "wight": "20"
+        },
+        {
+            "question": "5- تين ثينو (جمل)  تسميع 5 أرباع فقط  (5 *5 درجات )",
+            "wight": "25"
+        }
+    ]</t>
+  </si>
+  <si>
+    <t>[
+        {
+            "instructions": "في حالة وجود أي استفسار يُرجَي الرجوع لخدام المادة:+أ/ بيشوى منسى   أ/ كيرلس ميلاد    "
+        },
+        {
+            "question": "1- أونوف إممو ماريا   (تسميع جزء واحد فقط كاملاً )",
+            "wight": "30"
+        },
+        {
+            "question": "2- ذوكصولوجية كيهك الأولي (كيه غار آي شان)  تسميع 3 أرباع فقط  (3 *5 درجات )",
+            "wight": "15"
+        },
+        {
+            "question": "3- مرد إبركسيس عيد الميلاد",
+            "wight": "10"
+        },
+        {
+            "question": "4-  إى بارثيه نوس",
+            "wight": "20"
+        },
+        {
+            "question": "5- بي ﭼين ميسي",
+            "wight": "10"
+        },
+        {
+            "question": "6- لحن آبين شويس  لعيد الميلاد   (3 أرباع * 5  درجات )",
+            "wight": "15"
+        },
+        {
+            "question": "7- الهوس الثالث    تسميع 5 أرباع فقط  (5 *5 درجات )",
+            "wight": "25"
+        }
+    ]</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> [
+        {
+            "instructions": "في حالة وجود أي استفسار يُرجَي الرجوع لخدام المادة:+أ/ بيشوى منسى   أ/ كيرلس ميلاد    "
+        },
+        {
+            "question": "1-إبصالية آمويني تيرو لتسبحة عشيات آحاد كيهك    تسميع 5 أرباع فقط  (5 *5 درجات )",
+            "wight": "25"
+        },
+        {
+            "question": "2- ذوكصولوجية عيد الغطاس  تسميع 3 أرباع فقط  (3 *5 درجات )",
+            "wight": "15"
+        },
+        {
+            "question": "3- الهوس الرابع   تسميع 3 أرباع فقط من كل مزمور (3 * 3 * 5 درجات )",
+            "wight": "45"
+        }
+    ]</t>
+  </si>
+  <si>
+    <t>[
+        {
+            "instructions": "علي الخادم نُطْقْ الكلمة للمخدوم لأن المخدوم حافظ الكلمة سماعي فقط لا يستطيع القراءة+في حالة وجود أي استفسار يُرجَي الرجوع لخدام المادة:+ت/ مارينا فتح الله (01287124457))"
+        },
+        {
+            "question": "1- @ E0ovab @ معنى  كلمة  (  (  قديس - قدس - كنيسة)",
+            "wight": "5"
+        },
+        {
+            "question": "2- @ V @ كام قاعدة نطق لحرف   (  (  3 - 6 - 4)  ",
+            "wight": "5"
+        },
+        {
+            "question": "3-عدد حروف اللغة القبطية  (( 32 - 28 - 24)",
+            "wight": "5"
+        },
+        {
+            "question": "4- معنى كلمة سمكة (  @ T3bt @ - @  T3b @  - @ 2ai @)",
+            "wight": "5"
+        },
+        {
+            "question": "5- @ #i @ معنى  كلمة  (  (  حائط - بيت - حديقة)",
+            "wight": "5"
+        },
+        {
+            "question": "6-  كلمة ظلمة تعنى (( @ Jenea  @ - @  A7ioc @  - @ Xaki @)",
+            "wight": "5"
+        },
+        {
+            "question": "7-  يوم السبت معناها (( @ Piovai  @ - @  Pi2a24 @  - @ Pi2omt @)",
+            "wight": "5"
+        },
+        {
+            "question": "8-عدد حروف الحلقية  (( 5 - 4 - 3)",
+            "wight": "5"
+        },
+        {
+            "question": "9-   ب اذا جاء بعده حرف متحرك@B@ ينطق حرف    ((    )",
+            "wight": "5"
+        },
+        {
+            "question": "10-   من الحروف الحلقية@X@ حرف    ((    )",
+            "wight": "5"
+        },
+        {
+            "question": "11-   تعنى وردة@2ai@ كلمة    ((    )",
+            "wight": "5"
+        },
+        {
+            "question": "12- عدد الحروف الساكنة 25 حرف ((  )",
+            "wight": "5"
+        },
+        {
+            "question": "13- @ Piovai ((((@  يوم الاثنين معناه ((  )",
+            "wight": "5"
+        },
+        {
+            "question": "14- عدد الحروف المتحركة القابلة للكسر3 ((  )",
+            "wight": "5"
+        },
+        {
+            "question": "15-   تعنى ابن@Pi23ri@ كلمة    ((    )",
+            "wight": "5"
         }
     ]</t>
   </si>
@@ -354,7 +1777,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -368,6 +1791,21 @@
       <name val="Consolas"/>
       <family val="3"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -390,12 +1828,24 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1092,10 +2542,13 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AEAA58B4-CCC6-449D-B1B2-34A66B80EAA5}">
-  <dimension ref="A1:C25"/>
+  <dimension ref="A1:D74"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="4" max="4" width="8.88671875" style="4"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1106,270 +2559,751 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="C2">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="C3">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="C4">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>3</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="C5">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>3</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C6">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>3</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C7">
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>3</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C8">
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>3</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C9">
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
+        <v>3</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C10">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>3</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C11">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C12">
+        <v>1</v>
+      </c>
+      <c r="D12" s="3"/>
+    </row>
+    <row r="13" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>26</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C13">
+        <v>2</v>
+      </c>
+      <c r="D13" s="3"/>
+    </row>
+    <row r="14" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>26</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C14">
+        <v>3</v>
+      </c>
+      <c r="D14" s="3"/>
+    </row>
+    <row r="15" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>26</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C15">
         <v>4</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="D15" s="3"/>
+    </row>
+    <row r="16" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>26</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C16">
         <v>5</v>
       </c>
-      <c r="C10">
+      <c r="D16" s="3"/>
+    </row>
+    <row r="17" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>26</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C17">
+        <v>6</v>
+      </c>
+      <c r="D17" s="3"/>
+    </row>
+    <row r="18" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>26</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C18">
+        <v>7</v>
+      </c>
+      <c r="D18" s="3"/>
+    </row>
+    <row r="19" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>26</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C19">
+        <v>8</v>
+      </c>
+      <c r="D19" s="3"/>
+    </row>
+    <row r="20" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>26</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C20">
+        <v>9</v>
+      </c>
+      <c r="D20" s="3"/>
+    </row>
+    <row r="21" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>26</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C21">
+        <v>10</v>
+      </c>
+      <c r="D21" s="3"/>
+    </row>
+    <row r="22" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>26</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C22">
+        <v>11</v>
+      </c>
+      <c r="D22" s="3"/>
+    </row>
+    <row r="23" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>26</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C23">
+        <v>12</v>
+      </c>
+      <c r="D23" s="3"/>
+    </row>
+    <row r="24" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>26</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C24">
+        <v>13</v>
+      </c>
+      <c r="D24" s="3"/>
+    </row>
+    <row r="25" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>26</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C25">
+        <v>14</v>
+      </c>
+      <c r="D25" s="3"/>
+    </row>
+    <row r="26" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>26</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C26">
+        <v>15</v>
+      </c>
+      <c r="D26" s="3"/>
+    </row>
+    <row r="27" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>26</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C27">
+        <v>16</v>
+      </c>
+      <c r="D27" s="3"/>
+    </row>
+    <row r="28" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>26</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C28">
+        <v>17</v>
+      </c>
+      <c r="D28" s="3"/>
+    </row>
+    <row r="29" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>26</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="C29">
+        <v>18</v>
+      </c>
+      <c r="D29" s="3"/>
+    </row>
+    <row r="30" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>26</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="C30">
+        <v>19</v>
+      </c>
+      <c r="D30" s="3"/>
+    </row>
+    <row r="31" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>26</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="C31">
+        <v>20</v>
+      </c>
+      <c r="D31" s="3"/>
+    </row>
+    <row r="32" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>26</v>
+      </c>
+      <c r="B32" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="C32">
+        <v>21</v>
+      </c>
+      <c r="D32" s="3"/>
+    </row>
+    <row r="33" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>4</v>
+      </c>
+      <c r="B33" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="C33">
         <v>1</v>
       </c>
-    </row>
-    <row r="11" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
+      <c r="D33" s="3"/>
+    </row>
+    <row r="34" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
         <v>4</v>
       </c>
-      <c r="B11" s="1" t="s">
+      <c r="B34" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="C34">
+        <v>2</v>
+      </c>
+      <c r="D34" s="3"/>
+    </row>
+    <row r="35" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>4</v>
+      </c>
+      <c r="B35" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="C35">
+        <v>3</v>
+      </c>
+      <c r="D35" s="3"/>
+    </row>
+    <row r="36" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>4</v>
+      </c>
+      <c r="B36" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="C36">
+        <v>4</v>
+      </c>
+      <c r="D36" s="3"/>
+    </row>
+    <row r="37" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>4</v>
+      </c>
+      <c r="B37" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="C37">
         <v>5</v>
       </c>
-      <c r="C11">
+      <c r="D37" s="3"/>
+    </row>
+    <row r="38" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>4</v>
+      </c>
+      <c r="B38" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="C38">
+        <v>6</v>
+      </c>
+      <c r="D38" s="3"/>
+    </row>
+    <row r="39" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
+        <v>4</v>
+      </c>
+      <c r="B39" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="C39">
+        <v>7</v>
+      </c>
+      <c r="D39" s="3"/>
+    </row>
+    <row r="40" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
+        <v>4</v>
+      </c>
+      <c r="B40" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="C40">
+        <v>8</v>
+      </c>
+      <c r="D40" s="3"/>
+    </row>
+    <row r="41" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
+        <v>4</v>
+      </c>
+      <c r="B41" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="C41">
+        <v>9</v>
+      </c>
+      <c r="D41" s="6"/>
+    </row>
+    <row r="42" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
+        <v>4</v>
+      </c>
+      <c r="B42" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="C42">
+        <v>10</v>
+      </c>
+      <c r="D42" s="6"/>
+    </row>
+    <row r="43" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
+        <v>10</v>
+      </c>
+      <c r="B43" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="C43">
+        <v>1</v>
+      </c>
+      <c r="D43" s="3"/>
+    </row>
+    <row r="44" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
+        <v>10</v>
+      </c>
+      <c r="B44" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="C44">
         <v>2</v>
       </c>
-    </row>
-    <row r="12" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
+      <c r="D44" s="3"/>
+    </row>
+    <row r="45" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
+        <v>10</v>
+      </c>
+      <c r="B45" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C45">
+        <v>3</v>
+      </c>
+      <c r="D45" s="3"/>
+    </row>
+    <row r="46" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
+        <v>10</v>
+      </c>
+      <c r="B46" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="C46">
         <v>4</v>
       </c>
-      <c r="B12" s="1" t="s">
+      <c r="D46" s="3"/>
+    </row>
+    <row r="47" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
+        <v>10</v>
+      </c>
+      <c r="B47" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="C47">
+        <v>5</v>
+      </c>
+      <c r="D47" s="3"/>
+    </row>
+    <row r="48" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A48" t="s">
+        <v>10</v>
+      </c>
+      <c r="B48" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="C48">
         <v>6</v>
       </c>
-      <c r="C12">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
-        <v>4</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C13">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
-        <v>4</v>
-      </c>
-      <c r="B14" s="1" t="s">
+      <c r="D48" s="3"/>
+    </row>
+    <row r="49" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A49" t="s">
+        <v>10</v>
+      </c>
+      <c r="B49" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="C49">
         <v>7</v>
       </c>
-      <c r="C14">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
-        <v>4</v>
-      </c>
-      <c r="B15" s="1" t="s">
+      <c r="D49" s="3"/>
+    </row>
+    <row r="50" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A50" t="s">
+        <v>10</v>
+      </c>
+      <c r="B50" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="C50">
         <v>8</v>
       </c>
-      <c r="C15">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
-        <v>4</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C16">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
-        <v>4</v>
-      </c>
-      <c r="B17" s="1" t="s">
+      <c r="D50" s="3"/>
+    </row>
+    <row r="51" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A51" t="s">
+        <v>10</v>
+      </c>
+      <c r="B51" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C51">
         <v>9</v>
       </c>
-      <c r="C17">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
+      <c r="D51" s="3"/>
+    </row>
+    <row r="52" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A52" t="s">
         <v>10</v>
       </c>
-      <c r="B18" s="1" t="s">
+      <c r="B52" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C52">
+        <v>10</v>
+      </c>
+      <c r="D52" s="3"/>
+    </row>
+    <row r="53" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A53" t="s">
+        <v>10</v>
+      </c>
+      <c r="B53" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="C53">
         <v>11</v>
       </c>
-      <c r="C18">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
+      <c r="D53" s="3"/>
+    </row>
+    <row r="54" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A54" t="s">
         <v>10</v>
       </c>
-      <c r="B19" s="1" t="s">
+      <c r="B54" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="C54">
         <v>12</v>
       </c>
-      <c r="C19">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
+      <c r="D54" s="3"/>
+    </row>
+    <row r="55" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A55" t="s">
         <v>10</v>
       </c>
-      <c r="B20" s="1" t="s">
+      <c r="B55" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="C55">
         <v>13</v>
       </c>
-      <c r="C20">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" t="s">
+      <c r="D55" s="3"/>
+    </row>
+    <row r="56" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A56" t="s">
         <v>10</v>
       </c>
-      <c r="B21" s="1" t="s">
+      <c r="B56" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="C56">
         <v>14</v>
       </c>
-      <c r="C21">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" t="s">
+      <c r="D56" s="3"/>
+    </row>
+    <row r="57" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A57" t="s">
         <v>10</v>
       </c>
-      <c r="B22" s="1" t="s">
+      <c r="B57" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="C57">
         <v>15</v>
       </c>
-      <c r="C22">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" t="s">
+      <c r="D57" s="3"/>
+    </row>
+    <row r="58" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A58" t="s">
         <v>10</v>
       </c>
-      <c r="B23" s="1" t="s">
+      <c r="B58" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="C58">
         <v>16</v>
       </c>
-      <c r="C23">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" t="s">
+      <c r="D58" s="3"/>
+    </row>
+    <row r="59" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A59" t="s">
         <v>10</v>
       </c>
-      <c r="B24" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C24">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" t="s">
+      <c r="B59" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="C59">
+        <v>17</v>
+      </c>
+      <c r="D59" s="3"/>
+    </row>
+    <row r="60" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A60" t="s">
         <v>10</v>
       </c>
-      <c r="B25" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C25">
-        <v>8</v>
-      </c>
-    </row>
+      <c r="B60" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="C60">
+        <v>18</v>
+      </c>
+      <c r="D60" s="3"/>
+    </row>
+    <row r="61" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A61" t="s">
+        <v>10</v>
+      </c>
+      <c r="B61" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="C61">
+        <v>19</v>
+      </c>
+      <c r="D61" s="3"/>
+    </row>
+    <row r="62" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A62" t="s">
+        <v>10</v>
+      </c>
+      <c r="B62" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="C62">
+        <v>20</v>
+      </c>
+      <c r="D62" s="3"/>
+    </row>
+    <row r="63" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A63" t="s">
+        <v>10</v>
+      </c>
+      <c r="B63" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="C63">
+        <v>21</v>
+      </c>
+      <c r="D63" s="3"/>
+    </row>
+    <row r="64" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="65" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="66" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="67" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="68" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="69" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="70" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="71" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="72" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="73" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="74" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/exams_import.xlsx
+++ b/exams_import.xlsx
@@ -8,13 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\MY_WORK\peter\qr-exams-system\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F0E4E87-201E-4AC3-B9B6-E9ED99560508}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A1739E5-708C-4065-B6E2-04D3749E84A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="11520" windowHeight="12360" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2304" yWindow="2304" windowWidth="17280" windowHeight="8964" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="43">
   <si>
     <t>type</t>
   </si>
@@ -54,311 +53,7 @@
     <t>coptic</t>
   </si>
   <si>
-    <t>[         {             "question": "1- لحرف ده ” Ⲝ ” اسمه إيه ؟ \n إكسي",             "wight": "5"         },         {             "question": "2- يعني إيه كلمة ” لسان“ بالقبطي؟ \n Ⲗⲁⲥ",             "wight": "5"         },         {             "question": "3- يعني إيه كلمة اسم بالقبطي ؟\n Ⲣⲁⲛ",             "wight": "5"         },         {             "question": "4- يعني إيه كلمة كبير بالقبطي؟ \nⲚⲓϣϯ",             "wight": "5"         },         {             "question": "5- يعني إيه كلمة هدية بالقبطي ؟ \n Ⲧⲁⲓⲟ",             "wight": "5"         },         {             "question": "6- الحرف ده ” Ⲧ “ اسمه إيه؟ \n طاف",             "wight": "5"         },         {             "question": "7- يعني إيه كلمة أبي بالقبطي ؟\nⲠⲁⲓⲱⲧ",             "wight": "5"         },         {             "question": "8- يعني إيه كلمة مسطرة بالقبطي؟ \n ̀̀Ⲝⲟⲙⲏ",             "wight": "5"         },         {             "question": "9- يعني إيه كلمة دف بالقبطي؟\nⲔⲉⲙⲕⲉⲙ",             "wight": "5"         },         {             "question": "10- الحرف ده ” Ⲁ “اسمه إيه ؟\n الفا",             "wight": "5"         },         {             "question": "11- ̀يعني إيه كلمة عطشان بالقبطي؟  \nⲞⲃⲓ",             "wight": "5"         },         {             "question": "12- يعني إيه كلمة بندق بالقبطي؟ \nⲠⲁⲛⲦⲟⲕⲓ",             "wight": "5"         },         {             "question": "13- يعني إيه كلمة امى بالقبطي؟ \n Ⲧⲁⲙⲁⲩ",             "wight": "5"         },         {             "question": "14- يعني إيه كلمة اخى بالقبطي؟ \n Ⲡⲁⲥⲟⲛ",             "wight": "5"         },         {             "question": "15- يعني إيه كلمة سمسم بالقبطي؟ \n Ⲥⲓⲙⲥⲓⲙ",             "wight": "5"         },         {             "question": "16- الحرف ده ” Ⲙ “اسمه إيه ؟\n مى",             "wight": "5"         },         {             "question": "17- يعني إيه كلمة أختي بالقبطي؟ \n Ⲧⲁⲥⲱⲛⲓ",             "wight": "5"         },         {             "question": "18- يعني إيه كلمة أخوتي بالقبطي؟ \n Ⲛⲁ̀ⲥⲛⲏⲟⲩ",             "wight": "5"         },         {             "question": "19- الحرف ده ” Ⲟ “اسمه إيه ؟\n اوو",             "wight": "5"         },         {             "question": "20- يعني إيه كلمة Ⲙⲁϣϫ ؟ بالعربي\n اذن",             "wight": "5"         }     ]</t>
-  </si>
-  <si>
-    <t>[         {             "question": "1- حرف الـ ” Ⲡ “ يُْن َطق ..... \n ب",             "wight": "5"         },         {             "question": "2-  كلمة ” Ϯ ” معناها ... \n يعطى",             "wight": "5"         },         {             "question": "3-  كلمة شعر بالقبطي معناها ....\n ϥⲱⲓ",             "wight": "5"         },         {             "question": "4-  كلمة ” ⲩ ” معناها ... \n ى",             "wight": "5"         },         {             "question": "5-  اذكر حرف قبطي يُْن َطق )ف( واذكر كلمة قبطي مثال عليه\n ( Ⲫ - Ⲫⲉϧ) - (Ϥ - Ϥⲱⲓ)",             "wight": "5"         },         {             "question": "6-  كلمة ضلمة بالقبطي معناها .... \nⲬⲁⲕⲓ",             "wight": "5"         },         {             "question": "7-  كلمة Ⲯⲁⲗⲓⲥ بالعربي معناها ....... \nمقص",             "wight": "5"         },         {             "question": "8-  كلمة خبز بالقبطي معناها ..... \nⲰⲓⲕ",             "wight": "5"         },         {             "question": "9-  كلمة فحم بالقبطي معناها ..... \n Ϫⲉⲃⲥ",             "wight": "5"         },         {             "question": "10- كلمة امتحان بالقبطي معناها .\nϦⲟⲧϧⲉⲧ",             "wight": "5"         },         {             "question": "11- حرف الـ Ϩ يُْن َطق .. \n ه",             "wight": "5"         },         {             "question": "12- كلمة يسمع بالقبطي معناها ......... \nⲤⲱⲧⲉⲙ",             "wight": "5"         },         {             "question": "13- كلمة Ⲣⲓ بالعربي معناها ..... \nغرفة - حجرة",             "wight": "5"         },         {             "question": "14- كلمة يجلس بالقبطي معناها ......... \nϨⲉⲙⲥⲓ",             "wight": "5"         },         {             "question": "15- حرف الـ Ⲧ يُْن َطق .... وكلمة كرسي بالقبطي معناها .......... \nⲦⲟⲧⲥ - ت",             "wight": "5"         },         {             "question": "16- كلمة عيد بالقبطي معناها ............... وتبدأ بحرف\n Ϣ - Ϣⲁⲓ",             "wight": "5"         },         {             "question": "17- كلمة Ϭⲟⲓⲥ بالعربي معناها ........ \nرب",             "wight": "5"         },         {             "question": "11- حرف الـ Ϫ يُْن َطق .. \n ج",             "wight": "5"         },         {             "question": "19-  Ⲁⲣⲓ̀ϩⲙⲟⲧ اتفضل \n  ) Ⲟⲩϣⲉⲡ̀ϩⲙⲟⲧ : اإلجابة ).......................... شكرا",             "wight": "5"         },         {             "question": "20-  اسمك ايه ؟ ? Ⲡⲉⲕⲣⲁⲛ ⲟⲩ ?\nاسمي .......................... )اإلجابة : Ⲡⲁⲣⲁⲛ ⲡⲉ ) ",             "wight": "5"         }     ]</t>
-  </si>
-  <si>
-    <t>[         {             "question": "1- اذكر معنى الجملة الآتية بالعربي : أبانا الذي في السموات : Ⲡⲉⲛⲓⲱⲧ ⲉⲧϧⲉⲛ ⲛⲓⲫⲏⲟⲩ̀ⲓ",             "wight": "5"         },         {             "question": "2- اذكر معنى الجملة الآتية بالعربي : كذالك على الارض : Ⲛⲉⲙ ϩⲓϫⲉⲛ ⲡⲓⲕⲁϩⲓ",             "wight": "5"         },         {             "question": "3- اذكر معنى الجملة الآتية بالعربي : للمذنبين الينا : ̀Ⲛⲛⲏⲉ̀ⲧⲉ ⲟⲩⲟⲛ ̀ⲛⲧⲁⲛ ̀ⲉⲣⲱⲟⲩ",             "wight": "5"         },         {             "question": "4- اذكر معنى الجملة الآتية بالعربي : اعطه لنا اليوم : Ⲙⲏⲓϥ ⲛⲁⲛ ̀ⲙⲫⲟⲟⲩ",             "wight": "5"         },         {             "question": "5- اذكر معنى الجملة الآتية بالعربي : كما فى السماء : ̀Ⲙ̀ⲩⲣⲏϯ ϧⲉⲛ ̀ⲧⲫⲉ",             "wight": "5"         },         {             "question": "6- اذكر معنى الجملة الآتية بالقبطى : ليتقدس اسمك : Ⲙⲁⲣⲉⲛ ⲧⲟⲩⲃⲟ ̀ⲛϫⲉ ⲡⲉⲕⲣⲁⲛ",             "wight": "5"         },         {             "question": "7- اذكر معنى الجملة الآتية بالقبطى : خبزنا الذى للغد : Ⲡⲉⲛⲱⲓⲕ ̀ⲛⲧⲉ ⲣⲁⲥϯ",             "wight": "5"         },         {             "question": "8- اذكر معنى الجملة الآتية بالقبطى : لتكن نشيئتك : Ⲡⲉⲧⲉϩⲛⲁⲕ ⲙⲁⲣⲉϥϣⲱⲡⲓ",             "wight": "5"         },         {             "question": "9- اذكر معنى الجملة الآتية بالقبطى : ليأت ملكوتك : Ⲙⲁⲣⲉⲥ̀ⲓ ̀ⲛϫⲉ ⲧⲉⲕⲙⲉⲧⲟⲩⲣⲟ",             "wight": "5"         },         {             "question": "10- اذكر معنى الجملة الآتية بالقبطى : كما نغفر نحن ايضا : ̀ⲙ̀ⲩⲣⲏϯ ϩⲱⲛ ̀ⲛⲧⲉⲛⲭⲱ ⲉ̀ⲃⲟⲗ",             "wight": "5"         },         {             "question": "11- تسميع أبانا الذي بالقبطي كلها",             "wight": "25"         }     ]</t>
-  </si>
-  <si>
-    <t>[         {             "question": "1-  ما معنى الجملة الاتية : اعطه لنا اليوم\n Ⲙⲏⲓϥ ⲛⲁⲛ ̀ⲙⲫⲟⲟⲩ",             "wight": "5"         },         {             "question": "2-  ما معنى الجملة الاتية : و على الارض\n Ⲛⲉⲙ ϩⲓϫⲉⲛ Ⲡⲓⲕⲁϩⲓ",             "wight": "5"         },         {             "question": "3-  ما معنى الجملة الاتية : كما نغفر نحن ايضا\n ̀Ⲙ̀ⲫⲣⲏϯ ϩⲱⲛ ̀ⲛⲧⲉⲛⲕⲱ ̀ⲃⲟⲗ",             "wight": "5"         },         {             "question": "4-  ما معنى الجملة الاتية : Ⲙⲁⲣⲉϥⲧⲟⲩⲃⲟ ̀ⲛϫⲉ ⲡⲉⲕⲣⲁⲛ\n ليتقدس اسمك",             "wight": "5"         },         {             "question": "5-  ما معنى الجملة الاتية : ̀Ⲙ̀ⲫⲣⲏϯ ϧⲉⲛ ̀Ⲧⲫⲉ \n كما فى السماء",             "wight": "5"         },         {             "question": "6-  ما معنى الجملة الاتية : Ⲡⲉⲛⲱⲓⲕ ̀ⲛⲧⲉ ⲣⲁⲥϯ\n خبزنا الذى للغد",             "wight": "5"         },         {             "question": "7-  ما معنى الكلمة الاتية : Ⲡⲉⲧⲉϩⲛⲁⲕ\n مشيئتك",             "wight": "4"         },         {             "question": "8-  ما معنى الكلمة الاتية : Ⲡⲉⲛⲓⲱⲧ\n ابانا",             "wight": "4"         },         {             "question": "9-  ما معنى الكلمة الاتية : Ⲛⲓⲫⲏⲟⲩ̀ⲓ\n السموات",             "wight": "4"         },         {             "question": "10-  ما معنى الكلمة الاتية : Ⲣⲁⲥϯ\n الغد",             "wight": "4"         },         {             "question": "11-  ما معنى الكلمة الاتية : ̀Ⲙⲫⲟⲟⲩ\n اليوم",             "wight": "4"         },         {             "question": "12- اذكر قواعد الحروف اآلتية )يختار ٣ حروف فقط( : \n Ⲃ - Ⲯ - Ⲧ - Ⲩ - Ⲇ - Ⲥ - Ϣ",             "wight": "20"         },         {             "question": "13- س مع من إللي حفظناه في أبانا الذي: \n من اول Ⲡⲉⲧⲉϩⲛⲁⲕ ⲙⲁⲣⲉϥϣⲱⲡⲓ لحد  ̀Ⲙ̀ϥⲣⲏϯ ϩⲱⲛ ̀ⲛⲧⲉⲛⲭⲱ ⲉ̀ⲃⲟⲗ",             "wight": "10"         }     ]</t>
-  </si>
-  <si>
-    <t>[         {             "question": "1- اذكر معنى الجملة الآتية بالعربي : نحن عبيدك : Ⲁⲛⲟⲕ ϧⲁ ⲛⲉⲕⲉ̀ⲃⲓⲁⲓⲕ",             "wight": "10"         },         {             "question": "2- اذكر معنى الجملة الآتية بالعربي : يا الله اسمعنا : ̀Ⲫⲛⲟⲩϯ ⲥⲱⲧⲉⲙ ̀ⲉⲣⲟⲛ",             "wight": "10"         },         {             "question": "3- اذكر معنى الجملة الآتية بالعربي : تعهدنا بخلاصك : ϫⲉⲙⲡⲉⲛϣⲓⲛⲓ ϧⲉⲛ ⲡⲉⲕⲟⲩϫⲁⲓ",             "wight": "10"         },         {             "question": "4- اذكر معنى الجملة الآتية بالعربي : يا الله اطلع علينا :  ̀Ⲫⲛⲟⲩϯ ϫⲟⲩϣⲧ ̀ⲉⲣⲟⲛ",             "wight": "10"         },         {             "question": "5- اذكر معنى الجملة الآتية بالقبطى : مدرسة : Ⲁⲛⲍⲏⲃ",             "wight": "5"         },         {             "question": "6- اذكر معنى الجملة الآتية بالقبطى : رقم 9 : Ⲯⲓⲧ",             "wight": "5"         },         {             "question": "7- اذكر معنى الجملة الآتية بالقبطى : نحن : Ⲁⲛⲟⲛ",             "wight": "5"         },         {             "question": "8- اذكر معنى الجملة الآتية بالقبطى : ارحمنا : Ⲛⲁⲓ ⲛⲁⲛ",             "wight": "5"         },         {             "question": "9- اذكر معنى الجملة الآتية بالقبطى : مسمار : ̀Ⲓϥⲧ",             "wight": "5"         },         {             "question": "10- اذكر معنى الجملة الآتية بالقبطى : عالم : Ⲕⲟⲥⲙⲟⲥ",             "wight": "5"         },         {             "question": "11-  اذكر اسم وقاعدة الحروف الآ تية: ) 3 درجات لكل حرف( : Ϫ - Ⲃ - Ⳉ - Ⲇ - ϯ",             "wight": "15"         },         {             "question": "12- كم عدد الحروف اللى بنعرف منهم الكلمة القبطية؟ اذكر منهم 3  عددهم 7  ( Ϣ - Ϥ - Ϧ - Ϩ - Ϫ - Ϭ - ϯ )",             "wight": "2.5"         },         {             "question": "13- كم عدد الحروف اللى بنعرف منهم الكلمة اليونانية؟ اذكر منهم 2  عددهم 5   ( Ⳉ - Ⲇ - Ⲍ - Ⲝ - Ⲯ )",             "wight": "2.5"         },         {             "question": "14- ما هى النهايات ال 6 اللى بنعرف منهم الكلمة اليونانية؟  ( ⲁⲥ- ⲟⲥ - ⲏⲥ - ⲁⲛ - ⲟⲛ - ⲏⲛ)",             "wight": "2.5"         },         {             "question": "15-  ما هو الحرف القبطى اللى بيجى ساعات فى بداية الكلمات اليونانية ليعبر عن علامة التنفس الهائى؟  ( Ϩ )",             "wight": "2.5"         }     ]</t>
-  </si>
-  <si>
     <t>alhan</t>
-  </si>
-  <si>
-    <t>[         {             "question": "1- من مدائح الصوم الكبیر\n طوبى للرحماء على المساكین - المرد فقط",             "wight": "10"         },         {             "question": "2- مردات أناجیل قداس أحد الشعانین\n( 4 مردات * 10 درجات = 40)",             "wight": "40"         },         {             "question": "3- ذوكسابترى (التى تُقال بعد رفع الحمل)",             "wight": "10"         },         {             "question": "4-  آجيوس أو ثيه أوس\n( 4 أرباع * 5 درجات )",             "wight": "20"         }     ]</t>
-  </si>
-  <si>
-    <t>[         {             "question": "1-\tأيها الجلوس قفوا (قبطى)",             "wight": "5"         },         {             "question": "2- وإلى الشرق أنظروا (قبطى) ",             "wight": "5"         },         {             "question": "3- أُسجدوا لله بخوف ورعدة (قبطى) ",             "wight": "10"         },         {             "question": "4- ذوكسابترى (التى تُقال بعد رفع الحمل) ",             "wight": "10"         },         {             "question": "5-\tآجيوس أو ثيه أوس \n( 4 أرباع * 5 درجات )",             "wight": "20"         }     ]</t>
-  </si>
-  <si>
-    <t>[         {             "question": "1- كرحمتك يارب وليس كخطايانا",             "wight": "10"         },         {             "question": "2- مرد أوشية الرحمة\nإرحمنا يا الله الآب ضابط الكل (عربى وقبطى)\n(10 درجات للعربي + 10 درجات للقبطي )",             "wight": "20"         },         {             "question": "3- بركتهم المقدسة",             "wight": "10"         },         {             "question": "4-  كما كان هكذا يكون",             "wight": "10"         },         {             "question": "5- واحدٌ هو الآب القدوس",             "wight": "10"         }     ]</t>
-  </si>
-  <si>
-    <t>[         {             "question": "1-\tكرحمتك يارب وليس كخطايانا",             "wight": "10"         },         {             "question": "2- إنصتوا بحكمة الله (قبطى وعربى)\n(5 درجات للعربي + 10 درجات للقبطي )",             "wight": "15"         },         {             "question": "3- مرد أوشية الرحمة\nإرحمنا يا الله الآب ضابط الكل (عربى وقبطى)\n(10 درجات للعربي + 10 درجات للقبطي ) ",             "wight": "20"         },         {             "question": "4- بركتهم المقدسة ",             "wight": "10"         },         {             "question": "5- كما كان هكذا يكون ",             "wight": "10"         },         {             "question": "6-\tواحدٌ هو الآب القدوس ( الختام السريع ) ",             "wight": "10"         }     ]</t>
-  </si>
-  <si>
-    <t>[         {             "question": "1- مرد الإنجيل السنوى (أوأونياطو)\n( 4 أرباع * 5 درجات )",             "wight": "20"         },         {             "question": "2- ني شيه روبيم",             "wight": "15"         },         {             "question": "3- آمين(3) طون ثاناطون",             "wight": "20"         },         {             "question": "4- تين هوس إيه روك (قبطي وعربي)\n( 10 درجات قبطي +  10 درجات عربي)",             "wight": "20"         },         {             "question": "5- كاطاطو إيه ليه أوس",             "wight": "10"         },         {             "question": "6- إيريه بو إسمو إثؤواب",             "wight": "15"         },         {             "question": "7- تين جوشت إيـﭭول خا إتهى (عشية وباكر وقداس)\n(5 درجات لعشية وباكر + 10 درجات للقداس )",             "wight": "15"         }     ]</t>
-  </si>
-  <si>
-    <t>[         {             "question": "1-\tمرد دورة الحمل (صلوا من أجل هذه القرابين.....) قبطى وعربى\n(10 درجات للعربي + 10 درجات للقبطي )",             "wight": "20"         },         {             "question": "2- اطلبوا لكي يرحمنا الله ويتراءف علينا (قبطي وعربي)-ﻋﺸﻴﺔ وﺑﺎﻛﺮ وقداس\n(5 درجات للعربي)-ﻋﺸﻴﺔ وﺑﺎﻛﺮ + (10 درجات للقبطي )-ﻋﺸﻴﺔ وﺑﺎﻛﺮ\n(10 درجات للعربي)-قداس + (10 درجات للقبطي )-قداس",             "wight": "35"         },         {             "question": "3- هيتينية مارمرقس، هيتينية الشهيد إسطفانوس\n( 2 * 5 درجات = 10) ",             "wight": "10"         },         {             "question": "4- هيتينية مارجرجس، هيتينية أبو سيفين، هيتينية مارمينا\n( 3 * 5 درجات = 15) ",             "wight": "15"         },         {             "question": "5-\t هيتينية القديسة دميانة، هيتينية الأنبا بيشوى\n( 2 * 5 درجات = 10)",             "wight": "10"         },         {             "question": "6-\t  هيتينية الأنبا كاراس، هيتينية القديسين مكسيموس ودوماديوس\n( 2 * 5 درجات = 10)",             "wight": "10"         },         {             "question": "7-\t هيتينية قديسي اليوم، هيتينية البابا، هيتينيةالأسقف\n( 3 * 5 درجات = 15)",             "wight": "15"         }     ]</t>
-  </si>
-  <si>
-    <t>[         {             "question": "1-\tأوشية الزروع (عربي) - عشية وباكر وقداس\n(10 درجات عشية وباكر + 10 درجات قداس)",             "wight": "20"         },         {             "question": "2- أوشية أهوية السماء (عربي) - عشية وباكر وقداس\n(10 درجات عشية وباكر + 10 درجات قداس).",             "wight": "20"         },         {             "question": "3- أوشية المياة (عربي) - عشية وباكر وقداس\n(10 درجات عشية وباكر + 10 درجات قداس) ",             "wight": "20"         },         {             "question": "4-  آمين(3) طون ثاناطون  ",             "wight": "20"         },         {             "question": "5-\t تين هوس إيه روك (قبطي وعربي)\n( 10 درجات قبطي +  10 درجات عربي)",             "wight": "20"         },         {             "question": "6-\t كاطاطو إيه ليه أوس",             "wight": "10"         },         {             "question": "7-\t إيريه بو إسمو إثؤواب",             "wight": "15"         },         {             "question": "8-\t القارئون فليقولوا (قبطى وعربى)\n( 10 درجات قبطي +  10 درجات عربي)",             "wight": "20"         },         {             "question": "9-\t خلُصت حقاً ومع روحك (قبطى وعربى)\n( 10 درجات قبطي +  5  درجات عربي)",             "wight": "15"         },         {             "question": "10-\t الإعتراف الصغير (قبطي)",             "wight": "20"         }     ]</t>
-  </si>
-  <si>
-    <t>[
-        {
-            "instructions": "في حالة وجود أي استفسار يُرجَي الرجوع لخدام المادة:+أ/ بيشوي رضا حبيب: 01014222315 + أ/ إسحق إبراهيم: 01220068681"
-        },
-        {
-            "question": "1-\tفى الكنيسة (نصلى) و (نرنم) و (نتعلم)",
-            "wight": "2"
-        },
-        {
-            "question": "2- فرحت   (بالقائلين)  لى إلى  (بيت)  الرب  (نذهب) ",
-            "wight": "2"
-        },
-        {
-            "question": "3- أما أنا  (فبكثرة)  رحمتك  (أدخل)  بيتك و (أسجد)  قدام  (هيكل)  قدسك  (بمخافتك) ",
-            "wight": "2"
-        },
-        {
-            "question": "4- فى الكنيسة بنشوف أيقونات (بابا يسوع)   و(ماما العذراء)  و  (القديسين والقديسات) ",
-            "wight": "2"
-        },
-        {
-            "question": "5-\tالكنيسة هى بيتنا كلنا وبيت (الملائكة) و (القديسين) ",
-            "wight": "2"
-        },
-        {
-            "question": "6-\tمساكنك (محبوبة)  أيها الرب  إله (القوات) ",
-            "wight": "2"
-        },
-        {
-            "question": "7-\tلما بشوف الصينية والنجمة بافتكر (المذود)",
-            "wight": "2"
-        },
-        {
-            "question": "8-\tالشورية بتفكرنا لما كان بابا يسوع فى  (بطن ماما العذراء) ",
-            "wight": "2"
-        },
-        {
-            "question": "&lt;div&gt;&lt;span&gt;9-\t    &lt;/span&gt;&lt;img src='/admin/images/taks/01(1).jpg' &gt;&lt;/div&gt;",
-            "wight": "1"
-        },
-        {
-            "question": "&lt;div&gt;&lt;span&gt;10-\t    &lt;/span&gt;&lt;img src='/admin/images/taks/01(2).jpg' &gt;&lt;/div&gt;",
-            "wight": "1"
-        },
-        {
-            "question": "&lt;div&gt;&lt;span&gt;11-\t    &lt;/span&gt;&lt;img src='/admin/images/taks/01(3).jpg' &gt;&lt;/div&gt;",
-            "wight": "1"
-        },
-        {
-            "question": "&lt;div&gt;&lt;span&gt;12-\t    &lt;/span&gt;&lt;img src='/admin/images/taks/01(4).jpg' &gt;&lt;/div&gt;",
-            "wight": "1"
-        },
-        {
-            "question": "&lt;div&gt;&lt;span&gt;13-\t    &lt;/span&gt;&lt;img src='/admin/images/taks/01(5).jpg' &gt;&lt;/div&gt;",
-            "wight": "1"
-        },
-        {
-            "question": "&lt;div&gt;&lt;span&gt;14-\t    &lt;/span&gt;&lt;img src='/admin/images/taks/01(6).jpg' &gt;&lt;/div&gt;",
-            "wight": "1"
-        },
-        {
-            "question": "&lt;div&gt;&lt;span&gt;15-\t    &lt;/span&gt;&lt;img src='/admin/images/taks/01(7).jpg' &gt;&lt;/div&gt;",
-            "wight": "1"
-        },
-        {
-            "question": "&lt;div&gt;&lt;span&gt;16-\t    &lt;/span&gt;&lt;img src='/admin/images/taks/01(8).jpg' &gt;&lt;/div&gt;",
-            "wight": "1"
-        },
-        {
-            "question": "&lt;div&gt;&lt;span&gt;17-\t    &lt;/span&gt;&lt;img src='/admin/images/taks/01(9).jpg' &gt;&lt;/div&gt;",
-            "wight": "1"
-        },
-        {
-            "question": "&lt;div&gt;&lt;span&gt;18-\t    &lt;/span&gt;&lt;img src='/admin/images/taks/01(10).jpg' &gt;&lt;/div&gt;",
-            "wight": "1"
-        },
-        {
-            "question": "19-\tأبانا الذى فى السموات (بالعربي) ",
-            "wight": "10"
-        },
-        {
-            "question": "17-\tأبانا الذى فى السموات (بالقبطي) - الجزء الاول إلى (نان إيـﭭـول)",
-            "wight": "15"
-        }
-    ]</t>
-  </si>
-  <si>
-    <t>[
-        {
-            "instructions": "في حالة وجود أي استفسار يُرجَي الرجوع لخدام المادة:+أ/ بيشوي رضا حبيب 01014222315+أ/ إسحق إبراهيم 01220068681+أ/ چون عاطف 01284300589 "
-        },
-        {
-            "question": "1-\tعدد أسرار الكنيسة ( 4 – 5 – ..7.. )",
-            "wight": "2"
-        },
-        {
-            "question": "2-\tفي سر ( المعمودية – التناول – ..الزيجة.. ) يجمع فية ربنا اثنين ويوحدهم فى جسد واحد",
-            "wight": "2"
-        },
-        {
-            "question": "3-\tفى سر الميرون بنترشم  (33– 26 – ..36..)",
-            "wight": "2"
-        },
-        {
-            "question": "4-\tفي سر الكهنوت بيجي ........ ( الشماس – أبونا – ..المطران.. ) بيرشم إنسان ",
-            "wight": "2"
-        },
-        {
-            "question": "5-\tفي سر التوبة والاعتراف بنروح ........ ( لبابا – ماما – ..أبونا.. ) نعترف  بخطايانا",
-            "wight": "2"
-        },
-        {
-            "question": "6-\tسر التناول اسمه كمان سر ........... ( ..الشركة.. - الاعتراف – الزيجة )",
-            "wight": "2"
-        },
-        {
-            "question": "7-\tسر مسحة المرضة هو السر ........... ( الثاني – ..السابع.. – الخامس )",
-            "wight": "2"
-        },
-        {
-            "question": "8-\tاذكر أربعة من أسرار الكنيسة ؟\t\tالمعمودية – الميرون - التوبة والاعتراف – التناول - مسحة المرضي – الزيجة - الكهنوت",
-            "wight": "8"
-        },
-        {
-            "question": "9-\tتسميع السلام لك نسالك",
-            "wight": "15"
-        },
-        {
-            "question": "10-\tتسميع نعظمك يا ام النور الحقيقى",
-            "wight": "10"
-        }
-    ]</t>
-  </si>
-  <si>
-    <t>[
-        {
-            "instructions": "في حالة وجود أي استفسار يُرجَي الرجوع لخدام المادة:+أ/ چون عاطف 01284300589+أ/ ﭼون مجدي 01275034174 +أ/ ماركو ماهر 01221554457  "
-        },
-        {
-            "question": "1-\t ..يكون لون ستر الهيكل فى أسبوع الآلام   ..أسود..    وفى الخماسين    ..أبيض..   أما فى باقى الأيام ..أحمر",
-            "wight": "3"
-        },
-        {
-            "question": "2-\t  ..يعتبر أقدم بيت يجمع بين الله والإنسان هو  ..الفردوس",
-            "wight": "3"
-        },
-        {
-            "question": "3-\t\t...يفصل بين الهيكل والخورس    ...حامل الأيقونات",
-            "wight": "3"
-        },
-        {
-            "question": "4-\t .....أول كنيسة فى العالم كله هى بيت ......القديسة مريم والدة القديس مارمرقس ( العلية )",
-            "wight": "3"
-        },
-        {
-            "question": "5-  \t..إذا ما وقفنا فى هيكلك المقدس نُحسب كالقيام فى ..السماء ",
-            "wight": "3"
-        },
-        {
-            "question": "6- \tتُبْنَى الكنيسة حالياً على شكل سفينة\t(سفينة بطرس – ..فلك نوح.. – كل ماسبق)",
-            "wight": "3"
-        },
-        {
-            "question": "7-\t\tأغطية المذبح عددهم\t(اثنان – ..ثلاثة.. – خامسة)",
-            "wight": "3"
-        },
-        {
-            "question": "8- \tيوجد بالقسم الداخلي للكنيسة\t( الهيكل – الخورس – ..كل ماسبق..)",
-            "wight": "3"
-        },
-        {
-            "question": "9- \tداخل الهيكل نرى (دولاب الدياكونية – الدَرَج – الشرقية – المذبح – ..كل ما سبق..)",
-            "wight": "3"
-        },
-        {
-            "question": "10-    وظيفته حماية الكأس لئلا ينسكب\t(المستير – ..كرسي الكأس.. – المذبح)",
-            "wight": "3"
-        },
-        {
-            "question": "11-\tما هى الأشكال التي تُبْنَى عليها الكنيسة ؟ \t\tشكل السفينة      شكل الصليب       شكل الدائرة",
-            "wight": "4"
-        },
-        {
-            "question": "12-    ما هى أقسام الكنيسة من الداخل ؟\t\t\t     صحن الكنيسة        الخورس     الهيكل",
-            "wight": "4"
-        },
-        {
-            "question": "13-  \tلماذا ننظر ناحية الشرق فى صلواتنا؟\t\t     السيد المسيح صُلِبَ ناحية الشرق وسيأتى من الشرق",
-            "wight": "4"
-        },
-        {
-            "question": "14-  \tاذكر 5 أنواع من اللفائف في الكنيسة ؟\t\tلفافة الصنية - لفافة الحمل - لفافة الكاس - لفافة الكرسى – لفائف فرش المذبح - لفافة دورة الحمل - لفائف التناول",
-            "wight": "4"
-        },
-        {
-            "question": "15-    اذكر 5 من أدوات وأواني المذبح ؟\t              اللفائف – الصينية – الكأس – كرسى الكأس – المستير – القارورة – النجم - البشارة – درج البخور – الصليب",
-            "wight": "4"
-        },
-        {
-            "question": "16-\tتسميع قدوس، قدوس، قدوس، رب الصباؤوت",
-            "wight": "15"
-        },
-        {
-            "question": "17-\tتسميع فلنشكر صانع الخيرات إلي وعن موضعك المقدس هذا",
-            "wight": "10"
-        }
-    ]</t>
-  </si>
-  <si>
-    <t>[
-        {
-            "instructions": "في حالة وجود أي استفسار يُرجَي الرجوع لخدام المادة:+أ/ ﭼون مجدي 01275034174+أ/ ماركو ماهر 01221554457   "
-        },
-        {
-            "question": "1-\t مؤسس كل الأسرار هم التلاميذ وسلموها إلى من بعدهم  ( صح - ..خطأ..)",
-            "wight": "2"
-        },
-        {
-            "question": "2-\t يسمى سر الإفخارستيا بسر التناول وسر الأسرار  ( ..صح.. - خطأ)",
-            "wight": "2"
-        },
-        {
-            "question": "3-\t يتكون سر مسحة المرضى من 7 صلوات  ( ..صح.. - خطأ)",
-            "wight": "2"
-        },
-        {
-            "question": "4-\t سر الاعتراف لا يوجد له زمن أو ميعاد محدد  ( ..صح.. - خطأ)",
-            "wight": "2"
-        },
-        {
-            "question": "5-\t سر المعمودية له المرتبة الثانية بعد الكهنوت لأنه باب يدخل منه المؤمن إلى الكنيسة وملكوت النعمة  ( صح - ..خطأ..)",
-            "wight": "2"
-        },
-        {
-            "question": "6-\tمن إشارات المعمودية فى العهد القديم\t(..الطوفان.. – شجرة الحياة – لوحى الشريعة – مزامير داود)",
-            "wight": "4"
-        },
-        {
-            "question": "7-\tعدد رشومات زيت الميرون\t\t(37 رشمة – 140 رشمة – ..36 رشمة.. – 159 رشمة)",
-            "wight": "4"
-        },
-        {
-            "question": "8-\tالقناديل فى سر مسحة المرضى تكون\t(شمع – بخور - ..قطن..)",
-            "wight": "4"
-        },
-        {
-            "question": "9-\tأحضر زيت الميرون إلى مصر (البابا أثناسيوس الرسولى – البابا كيرلس عمود الدين – ..مار مرقس الرسول..)",
-            "wight": "4"
-        },
-        {
-            "question": "10- فى طقس الإكليل يوضع الإكليل على رأس (..الرجل والمرأة.. – المرأة فقط – الرجل فقط)",
-            "wight": "4"
-        },
-        {
-            "question": "11-\t  اشفوا مرضى ، طهروا برصاً ...  او  أية مدينة دخلتموها وقبلوكم .. فاشفوا المرضى الذين فيها  او أمريض أحد بينكم فليدع قسوس الكنيسة فيصلوا عليه ويدهنوه بزيت باسم الرب    --اذكر مما حفظت آية لسر مسحة المرضى؟ ",
-            "wight": "10"
-        },
-        {
-            "question": "12-    عَرِّف ماهو السر الكنسى؟   هو نعمة غير منظورة نحصل عليها بممارسة طقس منظور على يد كاهن شرعي بفعل الروح القدس",
-            "wight": "10"
-        },
-        {
-            "question": "13-  \tتسميع قانون الايمان",
-            "wight": "25"
-        }
-    ]</t>
   </si>
   <si>
     <t>[
@@ -1828,12 +1523,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2227,325 +1921,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F25"/>
-  <sheetFormatPr defaultColWidth="8.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="2" max="2" width="14.88671875" customWidth="1"/>
-    <col min="3" max="3" width="13.44140625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-    </row>
-    <row r="3" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C3">
-        <v>2</v>
-      </c>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2"/>
-    </row>
-    <row r="4" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C4">
-        <v>3</v>
-      </c>
-      <c r="D4" s="2"/>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2"/>
-    </row>
-    <row r="5" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C5">
-        <v>4</v>
-      </c>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
-      <c r="F5" s="2"/>
-    </row>
-    <row r="6" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>3</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C6">
-        <v>5</v>
-      </c>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
-      <c r="F6" s="2"/>
-    </row>
-    <row r="7" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>3</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C7">
-        <v>6</v>
-      </c>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
-      <c r="F7" s="2"/>
-    </row>
-    <row r="8" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>3</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C8">
-        <v>7</v>
-      </c>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
-      <c r="F8" s="2"/>
-    </row>
-    <row r="9" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>3</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="C9">
-        <v>8</v>
-      </c>
-      <c r="D9" s="2"/>
-      <c r="E9" s="2"/>
-      <c r="F9" s="2"/>
-    </row>
-    <row r="10" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>4</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>4</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C11">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
-        <v>4</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C12">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
-        <v>4</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C13">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
-        <v>4</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C14">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
-        <v>4</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C15">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
-        <v>4</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C16">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
-        <v>4</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C17">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
-        <v>10</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C18">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
-        <v>10</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C19">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
-        <v>10</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C20">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" t="s">
-        <v>10</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C21">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" t="s">
-        <v>10</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C22">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" t="s">
-        <v>10</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C23">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" t="s">
-        <v>10</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C24">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" t="s">
-        <v>10</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C25">
-        <v>8</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AEAA58B4-CCC6-449D-B1B2-34A66B80EAA5}">
   <dimension ref="A1:D74"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="4" max="4" width="8.88671875" style="4"/>
+    <col min="4" max="4" width="8.88671875" style="3"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -2564,7 +1944,7 @@
         <v>3</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="C2">
         <v>1</v>
@@ -2575,7 +1955,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="C3">
         <v>2</v>
@@ -2586,7 +1966,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="C4">
         <v>3</v>
@@ -2597,7 +1977,7 @@
         <v>3</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="C5">
         <v>4</v>
@@ -2608,7 +1988,7 @@
         <v>3</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="C6">
         <v>5</v>
@@ -2619,7 +1999,7 @@
         <v>3</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="C7">
         <v>6</v>
@@ -2630,7 +2010,7 @@
         <v>3</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="C8">
         <v>7</v>
@@ -2641,7 +2021,7 @@
         <v>3</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="C9">
         <v>8</v>
@@ -2652,7 +2032,7 @@
         <v>3</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="C10">
         <v>9</v>
@@ -2663,7 +2043,7 @@
         <v>3</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="C11">
         <v>10</v>
@@ -2671,627 +2051,627 @@
     </row>
     <row r="12" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="C12">
         <v>1</v>
       </c>
-      <c r="D12" s="3"/>
+      <c r="D12" s="2"/>
     </row>
     <row r="13" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="C13">
         <v>2</v>
       </c>
-      <c r="D13" s="3"/>
+      <c r="D13" s="2"/>
     </row>
     <row r="14" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="C14">
         <v>3</v>
       </c>
-      <c r="D14" s="3"/>
+      <c r="D14" s="2"/>
     </row>
     <row r="15" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="C15">
         <v>4</v>
       </c>
-      <c r="D15" s="3"/>
+      <c r="D15" s="2"/>
     </row>
     <row r="16" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="C16">
         <v>5</v>
       </c>
-      <c r="D16" s="3"/>
+      <c r="D16" s="2"/>
     </row>
     <row r="17" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="C17">
         <v>6</v>
       </c>
-      <c r="D17" s="3"/>
+      <c r="D17" s="2"/>
     </row>
     <row r="18" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="C18">
         <v>7</v>
       </c>
-      <c r="D18" s="3"/>
+      <c r="D18" s="2"/>
     </row>
     <row r="19" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="C19">
         <v>8</v>
       </c>
-      <c r="D19" s="3"/>
+      <c r="D19" s="2"/>
     </row>
     <row r="20" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="C20">
         <v>9</v>
       </c>
-      <c r="D20" s="3"/>
+      <c r="D20" s="2"/>
     </row>
     <row r="21" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="C21">
         <v>10</v>
       </c>
-      <c r="D21" s="3"/>
+      <c r="D21" s="2"/>
     </row>
     <row r="22" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="C22">
         <v>11</v>
       </c>
-      <c r="D22" s="3"/>
+      <c r="D22" s="2"/>
     </row>
     <row r="23" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="C23">
         <v>12</v>
       </c>
-      <c r="D23" s="3"/>
+      <c r="D23" s="2"/>
     </row>
     <row r="24" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="C24">
         <v>13</v>
       </c>
-      <c r="D24" s="3"/>
+      <c r="D24" s="2"/>
     </row>
     <row r="25" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="C25">
         <v>14</v>
       </c>
-      <c r="D25" s="3"/>
+      <c r="D25" s="2"/>
     </row>
     <row r="26" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="C26">
         <v>15</v>
       </c>
-      <c r="D26" s="3"/>
+      <c r="D26" s="2"/>
     </row>
     <row r="27" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>26</v>
-      </c>
-      <c r="B27" s="5" t="s">
-        <v>33</v>
+        <v>10</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>17</v>
       </c>
       <c r="C27">
         <v>16</v>
       </c>
-      <c r="D27" s="3"/>
+      <c r="D27" s="2"/>
     </row>
     <row r="28" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>26</v>
-      </c>
-      <c r="B28" s="5" t="s">
-        <v>33</v>
+        <v>10</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>17</v>
       </c>
       <c r="C28">
         <v>17</v>
       </c>
-      <c r="D28" s="3"/>
+      <c r="D28" s="2"/>
     </row>
     <row r="29" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>26</v>
-      </c>
-      <c r="B29" s="5" t="s">
-        <v>34</v>
+        <v>10</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>18</v>
       </c>
       <c r="C29">
         <v>18</v>
       </c>
-      <c r="D29" s="3"/>
+      <c r="D29" s="2"/>
     </row>
     <row r="30" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>26</v>
-      </c>
-      <c r="B30" s="5" t="s">
-        <v>35</v>
+        <v>10</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>19</v>
       </c>
       <c r="C30">
         <v>19</v>
       </c>
-      <c r="D30" s="3"/>
+      <c r="D30" s="2"/>
     </row>
     <row r="31" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>26</v>
-      </c>
-      <c r="B31" s="5" t="s">
-        <v>36</v>
+        <v>10</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>20</v>
       </c>
       <c r="C31">
         <v>20</v>
       </c>
-      <c r="D31" s="3"/>
+      <c r="D31" s="2"/>
     </row>
     <row r="32" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>26</v>
-      </c>
-      <c r="B32" s="5" t="s">
-        <v>36</v>
+        <v>10</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>20</v>
       </c>
       <c r="C32">
         <v>21</v>
       </c>
-      <c r="D32" s="3"/>
+      <c r="D32" s="2"/>
     </row>
     <row r="33" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>4</v>
       </c>
-      <c r="B33" s="5" t="s">
-        <v>37</v>
+      <c r="B33" s="4" t="s">
+        <v>21</v>
       </c>
       <c r="C33">
         <v>1</v>
       </c>
-      <c r="D33" s="3"/>
+      <c r="D33" s="2"/>
     </row>
     <row r="34" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>4</v>
       </c>
-      <c r="B34" s="5" t="s">
-        <v>37</v>
+      <c r="B34" s="4" t="s">
+        <v>21</v>
       </c>
       <c r="C34">
         <v>2</v>
       </c>
-      <c r="D34" s="3"/>
+      <c r="D34" s="2"/>
     </row>
     <row r="35" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>4</v>
       </c>
-      <c r="B35" s="5" t="s">
-        <v>37</v>
+      <c r="B35" s="4" t="s">
+        <v>21</v>
       </c>
       <c r="C35">
         <v>3</v>
       </c>
-      <c r="D35" s="3"/>
+      <c r="D35" s="2"/>
     </row>
     <row r="36" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>4</v>
       </c>
-      <c r="B36" s="5" t="s">
-        <v>38</v>
+      <c r="B36" s="4" t="s">
+        <v>22</v>
       </c>
       <c r="C36">
         <v>4</v>
       </c>
-      <c r="D36" s="3"/>
+      <c r="D36" s="2"/>
     </row>
     <row r="37" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>4</v>
       </c>
-      <c r="B37" s="5" t="s">
-        <v>38</v>
+      <c r="B37" s="4" t="s">
+        <v>22</v>
       </c>
       <c r="C37">
         <v>5</v>
       </c>
-      <c r="D37" s="3"/>
+      <c r="D37" s="2"/>
     </row>
     <row r="38" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>4</v>
       </c>
-      <c r="B38" s="5" t="s">
-        <v>38</v>
+      <c r="B38" s="4" t="s">
+        <v>22</v>
       </c>
       <c r="C38">
         <v>6</v>
       </c>
-      <c r="D38" s="3"/>
+      <c r="D38" s="2"/>
     </row>
     <row r="39" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>4</v>
       </c>
-      <c r="B39" s="5" t="s">
-        <v>38</v>
+      <c r="B39" s="4" t="s">
+        <v>22</v>
       </c>
       <c r="C39">
         <v>7</v>
       </c>
-      <c r="D39" s="3"/>
+      <c r="D39" s="2"/>
     </row>
     <row r="40" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>4</v>
       </c>
-      <c r="B40" s="5" t="s">
-        <v>58</v>
+      <c r="B40" s="4" t="s">
+        <v>42</v>
       </c>
       <c r="C40">
         <v>8</v>
       </c>
-      <c r="D40" s="3"/>
+      <c r="D40" s="2"/>
     </row>
     <row r="41" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>4</v>
       </c>
-      <c r="B41" s="5" t="s">
-        <v>58</v>
+      <c r="B41" s="4" t="s">
+        <v>42</v>
       </c>
       <c r="C41">
         <v>9</v>
       </c>
-      <c r="D41" s="6"/>
+      <c r="D41" s="5"/>
     </row>
     <row r="42" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>4</v>
       </c>
-      <c r="B42" s="5" t="s">
-        <v>58</v>
+      <c r="B42" s="4" t="s">
+        <v>42</v>
       </c>
       <c r="C42">
         <v>10</v>
       </c>
-      <c r="D42" s="6"/>
+      <c r="D42" s="5"/>
     </row>
     <row r="43" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>10</v>
-      </c>
-      <c r="B43" s="5" t="s">
-        <v>39</v>
+        <v>5</v>
+      </c>
+      <c r="B43" s="4" t="s">
+        <v>23</v>
       </c>
       <c r="C43">
         <v>1</v>
       </c>
-      <c r="D43" s="3"/>
+      <c r="D43" s="2"/>
     </row>
     <row r="44" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>10</v>
-      </c>
-      <c r="B44" s="5" t="s">
-        <v>40</v>
+        <v>5</v>
+      </c>
+      <c r="B44" s="4" t="s">
+        <v>24</v>
       </c>
       <c r="C44">
         <v>2</v>
       </c>
-      <c r="D44" s="3"/>
+      <c r="D44" s="2"/>
     </row>
     <row r="45" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>10</v>
-      </c>
-      <c r="B45" s="5" t="s">
-        <v>41</v>
+        <v>5</v>
+      </c>
+      <c r="B45" s="4" t="s">
+        <v>25</v>
       </c>
       <c r="C45">
         <v>3</v>
       </c>
-      <c r="D45" s="3"/>
+      <c r="D45" s="2"/>
     </row>
     <row r="46" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>10</v>
-      </c>
-      <c r="B46" s="5" t="s">
-        <v>42</v>
+        <v>5</v>
+      </c>
+      <c r="B46" s="4" t="s">
+        <v>26</v>
       </c>
       <c r="C46">
         <v>4</v>
       </c>
-      <c r="D46" s="3"/>
+      <c r="D46" s="2"/>
     </row>
     <row r="47" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>10</v>
-      </c>
-      <c r="B47" s="5" t="s">
-        <v>42</v>
+        <v>5</v>
+      </c>
+      <c r="B47" s="4" t="s">
+        <v>26</v>
       </c>
       <c r="C47">
         <v>5</v>
       </c>
-      <c r="D47" s="3"/>
+      <c r="D47" s="2"/>
     </row>
     <row r="48" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>10</v>
-      </c>
-      <c r="B48" s="5" t="s">
-        <v>43</v>
+        <v>5</v>
+      </c>
+      <c r="B48" s="4" t="s">
+        <v>27</v>
       </c>
       <c r="C48">
         <v>6</v>
       </c>
-      <c r="D48" s="3"/>
+      <c r="D48" s="2"/>
     </row>
     <row r="49" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>10</v>
-      </c>
-      <c r="B49" s="5" t="s">
-        <v>44</v>
+        <v>5</v>
+      </c>
+      <c r="B49" s="4" t="s">
+        <v>28</v>
       </c>
       <c r="C49">
         <v>7</v>
       </c>
-      <c r="D49" s="3"/>
+      <c r="D49" s="2"/>
     </row>
     <row r="50" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>10</v>
-      </c>
-      <c r="B50" s="5" t="s">
-        <v>45</v>
+        <v>5</v>
+      </c>
+      <c r="B50" s="4" t="s">
+        <v>29</v>
       </c>
       <c r="C50">
         <v>8</v>
       </c>
-      <c r="D50" s="3"/>
+      <c r="D50" s="2"/>
     </row>
     <row r="51" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>10</v>
-      </c>
-      <c r="B51" s="5" t="s">
-        <v>46</v>
+        <v>5</v>
+      </c>
+      <c r="B51" s="4" t="s">
+        <v>30</v>
       </c>
       <c r="C51">
         <v>9</v>
       </c>
-      <c r="D51" s="3"/>
+      <c r="D51" s="2"/>
     </row>
     <row r="52" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>10</v>
-      </c>
-      <c r="B52" s="5" t="s">
-        <v>47</v>
+        <v>5</v>
+      </c>
+      <c r="B52" s="4" t="s">
+        <v>31</v>
       </c>
       <c r="C52">
         <v>10</v>
       </c>
-      <c r="D52" s="3"/>
+      <c r="D52" s="2"/>
     </row>
     <row r="53" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>10</v>
-      </c>
-      <c r="B53" s="5" t="s">
-        <v>48</v>
+        <v>5</v>
+      </c>
+      <c r="B53" s="4" t="s">
+        <v>32</v>
       </c>
       <c r="C53">
         <v>11</v>
       </c>
-      <c r="D53" s="3"/>
+      <c r="D53" s="2"/>
     </row>
     <row r="54" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>10</v>
-      </c>
-      <c r="B54" s="5" t="s">
-        <v>49</v>
+        <v>5</v>
+      </c>
+      <c r="B54" s="4" t="s">
+        <v>33</v>
       </c>
       <c r="C54">
         <v>12</v>
       </c>
-      <c r="D54" s="3"/>
+      <c r="D54" s="2"/>
     </row>
     <row r="55" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>10</v>
-      </c>
-      <c r="B55" s="5" t="s">
-        <v>50</v>
+        <v>5</v>
+      </c>
+      <c r="B55" s="4" t="s">
+        <v>34</v>
       </c>
       <c r="C55">
         <v>13</v>
       </c>
-      <c r="D55" s="3"/>
+      <c r="D55" s="2"/>
     </row>
     <row r="56" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>10</v>
-      </c>
-      <c r="B56" s="5" t="s">
-        <v>51</v>
+        <v>5</v>
+      </c>
+      <c r="B56" s="4" t="s">
+        <v>35</v>
       </c>
       <c r="C56">
         <v>14</v>
       </c>
-      <c r="D56" s="3"/>
+      <c r="D56" s="2"/>
     </row>
     <row r="57" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>10</v>
-      </c>
-      <c r="B57" s="5" t="s">
-        <v>52</v>
+        <v>5</v>
+      </c>
+      <c r="B57" s="4" t="s">
+        <v>36</v>
       </c>
       <c r="C57">
         <v>15</v>
       </c>
-      <c r="D57" s="3"/>
+      <c r="D57" s="2"/>
     </row>
     <row r="58" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>10</v>
-      </c>
-      <c r="B58" s="5" t="s">
-        <v>53</v>
+        <v>5</v>
+      </c>
+      <c r="B58" s="4" t="s">
+        <v>37</v>
       </c>
       <c r="C58">
         <v>16</v>
       </c>
-      <c r="D58" s="3"/>
+      <c r="D58" s="2"/>
     </row>
     <row r="59" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>10</v>
-      </c>
-      <c r="B59" s="5" t="s">
-        <v>54</v>
+        <v>5</v>
+      </c>
+      <c r="B59" s="4" t="s">
+        <v>38</v>
       </c>
       <c r="C59">
         <v>17</v>
       </c>
-      <c r="D59" s="3"/>
+      <c r="D59" s="2"/>
     </row>
     <row r="60" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>10</v>
-      </c>
-      <c r="B60" s="5" t="s">
-        <v>55</v>
+        <v>5</v>
+      </c>
+      <c r="B60" s="4" t="s">
+        <v>39</v>
       </c>
       <c r="C60">
         <v>18</v>
       </c>
-      <c r="D60" s="3"/>
+      <c r="D60" s="2"/>
     </row>
     <row r="61" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>10</v>
-      </c>
-      <c r="B61" s="5" t="s">
-        <v>56</v>
+        <v>5</v>
+      </c>
+      <c r="B61" s="4" t="s">
+        <v>40</v>
       </c>
       <c r="C61">
         <v>19</v>
       </c>
-      <c r="D61" s="3"/>
+      <c r="D61" s="2"/>
     </row>
     <row r="62" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>10</v>
-      </c>
-      <c r="B62" s="5" t="s">
-        <v>56</v>
+        <v>5</v>
+      </c>
+      <c r="B62" s="4" t="s">
+        <v>40</v>
       </c>
       <c r="C62">
         <v>20</v>
       </c>
-      <c r="D62" s="3"/>
+      <c r="D62" s="2"/>
     </row>
     <row r="63" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>10</v>
-      </c>
-      <c r="B63" s="5" t="s">
-        <v>57</v>
+        <v>5</v>
+      </c>
+      <c r="B63" s="4" t="s">
+        <v>41</v>
       </c>
       <c r="C63">
         <v>21</v>
       </c>
-      <c r="D63" s="3"/>
+      <c r="D63" s="2"/>
     </row>
     <row r="64" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="65" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
